--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,9 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
   </fonts>
@@ -118,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -168,6 +172,8 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3246,7 +3252,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate-rdfs:comment</t>
+          <t>hasCatholyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4608,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate-rdfs:comment</t>
+          <t>hasAnolyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -5900,6 +5906,238 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Include this info (yes/no) Test becomes root object, not cell</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Example dataset title</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What the dataset contains, and anything needed to read it correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Keywords</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>redox flow battery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>electrochemical cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Date issued</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Date published</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Publication DOI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1234/example.2026.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Dataset URL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Dataset API URL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Citation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F. Lastname et al., Example Journal 1, 100 (2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Figures</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fig. 1a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fig. 2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Affiliations</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Firstname Lastname</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6013,7 +6251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6212,13 +6450,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6312,182 +6550,206 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fuel Cell Technologies</t>
+          <t>FlowCell</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fumatech</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Fuel Cell Technologies</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Fumatech</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30254565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TitaniumDioxide</t>
+          <t>Graphite</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>Bismuth</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pinflow</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q114797344</t>
+          <t>TitaniumDioxide</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PorousElectrode</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SGL Carbon</t>
+          <t>Pinflow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q320207</t>
+          <t>https://www.wikidata.org/wiki/Q114797344</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SigmaAldrich</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q680841</t>
+          <t>PorousElectrode</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>SGL Carbon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q643674</t>
+          <t>https://www.wikidata.org/wiki/Q320207</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>SigmaAldrich</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q680841</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Viton</t>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q643674</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PotassiumSaltCompound</t>
+          <t>Viton</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PolymerCompound</t>
+          <t>PolyetherEtherKetone</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OrganicAcid</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Argon</t>
+          <t>PolymerCompound</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>OrganicAcid</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
@@ -6498,7 +6760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,9 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <sz val="11"/>
     </font>
   </fonts>
@@ -118,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -168,6 +172,8 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5961,6 +5967,238 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Include this info (yes/no) Test becomes root object</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Example dataset title</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>What the dataset contains, and anything needed to read it correctly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Keywords</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>redox flow battery</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>electrochemical cell</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Publisher</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>License</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Date issued</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Date published</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Publication DOI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1234/example.2026.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Dataset URL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Dataset API URL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/1234567</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Citation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F. Lastname et al., Example Journal 1, 100 (2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Figures</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fig. 1a</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fig. 2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Authors</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>Affiliations</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Firstname Lastname</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6069,7 +6307,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6268,13 +6506,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6368,182 +6606,206 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>ETH Zurich</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fuel Cell Technologies</t>
+          <t>FlowCell</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fumatech</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Fuel Cell Technologies</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Fumatech</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30254565</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TitaniumDioxide</t>
+          <t>Graphite</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>Bismuth</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pinflow</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q114797344</t>
+          <t>TitaniumDioxide</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PorousElectrode</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SGL Carbon</t>
+          <t>Pinflow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q320207</t>
+          <t>https://www.wikidata.org/wiki/Q114797344</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SigmaAldrich</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q680841</t>
+          <t>PorousElectrode</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>SGL Carbon</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q643674</t>
+          <t>https://www.wikidata.org/wiki/Q320207</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>SigmaAldrich</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q680841</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Viton</t>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q643674</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PotassiumSaltCompound</t>
+          <t>Viton</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PolymerCompound</t>
+          <t>PolyetherEtherKetone</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OrganicAcid</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Argon</t>
+          <t>PolymerCompound</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>OrganicAcid</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
@@ -6554,7 +6816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -848,7 +848,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0.1.3</t>
+          <t>0.1.4</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate</t>
+          <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate</t>
+          <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-schema:manufacturer</t>
+          <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-schema:productID</t>
+          <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Thickness</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Porosity</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Area</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Area</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Thickness</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Weight</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate</t>
+          <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate</t>
+          <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-schema:manufacturer</t>
+          <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-schema:productID</t>
+          <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Thickness</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-rdfs:comment</t>
+          <t>hasNegativeElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       <c r="E47" s="11" t="n"/>
       <c r="F47" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Porosity</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Area</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Area</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       <c r="E49" s="11" t="n"/>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Thickness</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Weight</t>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode-Substrate-rdfs:comment</t>
+          <t>hasNegativeElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate-rdfs:comment</t>
+          <t>hasCatholyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate-rdfs:comment</t>
+          <t>hasAnolyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5489,7 @@
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Flowfield materail chemical formula</t>
+          <t>Flowfield material chemical formula</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasSubstrate-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -1291,15 +1291,17 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode weight</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>53.2</v>
+          <t>Positive electrode substrate thickness in cell comment</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Thickness under compression</t>
+        </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>mg</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1310,51 +1312,45 @@
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Positive electrode substrate treatment (Untreated, Chemical, Thermal)</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Untreated electrode</t>
-        </is>
+          <t>Positive electrode weight</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>53.2</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mg</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasSubstrate-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material type</t>
+          <t>Positive electrode substrate treatment (Untreated, Chemical, Thermal)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>Untreated electrode</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1364,25 +1360,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
+          <t>hasPositiveElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material class</t>
+          <t>Positive electrode coating active material type</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>TitaniumDioxide</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1395,11 +1395,7 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
@@ -1409,12 +1405,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material chemical name</t>
+          <t>Positive electrode coating active material class</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Titanium dioxide</t>
+          <t>TitaniumDioxide</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1429,24 +1425,24 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material chemical formula</t>
+          <t>Positive electrode coating active material chemical name</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>TiO2</t>
+          <t>Titanium dioxide</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1466,19 +1462,19 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material description</t>
+          <t>Positive electrode coating active material chemical formula</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Liquid-phase deposition using a mixed solution of H3BO3 and (NH4)2TiF6</t>
+          <t>TiO2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1493,774 +1489,778 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Describe catalyst deposition procedure</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>Positive electrode coating active material description</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Liquid-phase deposition using a mixed solution of H3BO3 and (NH4)2TiF6</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Describe catalyst deposition procedure</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>Positive electrode coating active material mass loading</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B35" s="4" t="n">
         <v>1.3579</v>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>mg/cm2</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Negative electrode</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Negative electrode type</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>PorousElectrode</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Pristine</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate type</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>CarbonPaper, CarbonFelt, CarbonCloth etc.</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate material class</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate material chemical name</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate material chemical formula</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>SGL Carbon</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="inlineStr">
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate product ID</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Sigracet 39AA</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate thickness</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B46" s="11" t="n">
         <v>560</v>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate thickness comment</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Used two 280 µm carbon papers</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Describe stacking of multiple electrode components or if single elctrode was used</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Negative electrode substrate porosity</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode geometric area</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>Negative electrode thickness in cell (including compression)</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>450</v>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>um</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode substrate thickness in cell comment</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Thickness under compression</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>Negative electrode weight</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode substrate treatment (Untreated, Chemical, Thermal)</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Untreated electrode</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode substrate porosity</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="C47" s="11" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material type</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Electrocatalyst</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode geometric area</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>cm2</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode thickness in cell (including compression)</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="C49" s="11" t="inlineStr">
-        <is>
-          <t>um</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode weight</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n">
-        <v>52.3</v>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>mg</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode substrate treatment (Untreated, Chemical, Thermal)</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Untreated electrode</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E51" s="11" t="inlineStr">
-        <is>
-          <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
-        </is>
-      </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasSubstrate-rdfs:comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material type</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>Electrocatalyst</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material class</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Bismuth</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Ontology term, be as specific as possible</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material class</t>
-        </is>
-      </c>
-      <c r="B53" s="11" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material chemical name</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material chemical name</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Bismuth</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material chemical formula</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Bi</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material chemical formula</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>Bi</t>
-        </is>
-      </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Negative electrode coating active material description</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Deposited from BiCl3 solution</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material description</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Deposited from BiCl3 solution</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>Describe catalyst deposition procedure</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-rdfs:comment</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material mass loading</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>1.23456</v>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>mg/cm2</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrolyte / posolyte / catholyte</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
+          <t>Negative electrode coating active material mass loading</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>1.23456</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mg/cm2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-schema:manufacturer</t>
+          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Positive electrolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Posolyte 0.5M</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>hasCatholyte-schema:productID</t>
-        </is>
-      </c>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrolyte / posolyte / catholyte</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A class</t>
+          <t>Positive electrolyte manufacturer</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2273,26 +2273,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
+          <t>hasCatholyte-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A chemical name</t>
+          <t>Positive electrolyte manufacturer product ID</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Posolyte 0.5M</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -2302,29 +2298,25 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A chemical formula</t>
+          <t>Positive electrolyte solvent A class</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>H2O</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2339,50 +2331,56 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A purity</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="n">
-        <v>100</v>
+          <t>Positive electrolyte solvent A chemical name</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A purity considered in calculation?</t>
+          <t>Positive electrolyte solvent A chemical formula</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>H2O</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2392,24 +2390,24 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-rdfs:comment</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A volume fraction</t>
+          <t>Positive electrolyte solvent A purity</t>
         </is>
       </c>
       <c r="B66" s="14" t="n">
@@ -2422,25 +2420,25 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E66" s="14" t="n"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A manufacturer</t>
+          <t>Positive electrolyte solvent A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2453,48 +2451,54 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E67" s="4" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>MilliQ</t>
-        </is>
+          <t>Positive electrolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E68" s="14" t="n"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B class</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
+          <t>Positive electrolyte solvent A manufacturer</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2502,27 +2506,27 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B chemical name</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="n"/>
+          <t>Positive electrolyte solvent A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>MilliQ</t>
+        </is>
+      </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2533,21 +2537,17 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E70" s="14" t="n"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B chemical formula</t>
+          <t>Positive electrolyte solvent B class</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B purity</t>
+          <t>Positive electrolyte solvent B chemical name</t>
         </is>
       </c>
       <c r="B72" s="14" t="n"/>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
@@ -2589,17 +2589,21 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E72" s="14" t="n"/>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B purity considered in calculation?</t>
+          <t>Positive electrolyte solvent B chemical formula</t>
         </is>
       </c>
       <c r="B73" s="4" t="n"/>
@@ -2615,24 +2619,22 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B74" s="14" t="n">
-        <v>0</v>
-      </c>
+          <t>Positive electrolyte solvent B purity</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n"/>
       <c r="C74" s="14" t="inlineStr">
         <is>
           <t>%</t>
@@ -2640,20 +2642,20 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E74" s="14" t="n"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B manufacturer</t>
+          <t>Positive electrolyte solvent B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
@@ -2667,48 +2669,50 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="n"/>
+          <t>Positive electrolyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E76" s="14" t="n"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A class</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
+          <t>Positive electrolyte solvent B manufacturer</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
       <c r="C77" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2716,31 +2720,23 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A chemical name</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>Potassium ferrocyanide trihydrate</t>
-        </is>
-      </c>
+          <t>Positive electrolyte solvent B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n"/>
       <c r="C78" s="14" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2748,29 +2744,25 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="n"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A chemical formula</t>
+          <t>Positive electrolyte solute A class</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>K4Fe(CN)6 * 3 H2O</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2780,32 +2772,34 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A purity</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="n">
-        <v>99</v>
+          <t>Positive electrolyte solute A chemical name</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Potassium ferrocyanide trihydrate</t>
+        </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -2813,22 +2807,26 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E80" s="14" t="n"/>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A purity considered in calculation?</t>
+          <t>Positive electrolyte solute A chemical formula</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>K4Fe(CN)6 * 3 H2O</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2843,50 +2841,50 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-rdfs:comment</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive electrolyte solute A molarity </t>
+          <t>Positive electrolyte solute A purity</t>
         </is>
       </c>
       <c r="B82" s="14" t="n">
-        <v>0.5</v>
+        <v>99</v>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E82" s="14" t="n"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A manufacturer</t>
+          <t>Positive electrolyte solute A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2899,48 +2897,52 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A manufacturer productD</t>
+          <t xml:space="preserve">Positive electrolyte solute A molarity </t>
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>10504474</v>
+        <v>0.5</v>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E84" s="14" t="n"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B class</t>
+          <t>Positive electrolyte solute A manufacturer</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>PotassiumSaltCompound</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2950,30 +2952,24 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B chemical name</t>
-        </is>
-      </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>Potassium ferricyanide</t>
-        </is>
+          <t>Positive electrolyte solute A manufacturer productD</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>10504474</v>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
@@ -2982,29 +2978,25 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B chemical formula</t>
+          <t>Positive electrolyte solute B class</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>K3Fe(CN)6</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3019,27 +3011,29 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B purity</t>
-        </is>
-      </c>
-      <c r="B88" s="14" t="n">
-        <v>98</v>
+          <t>Positive electrolyte solute B chemical name</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>Potassium ferricyanide</t>
+        </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -3047,22 +3041,26 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E88" s="14" t="n"/>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B purity considered in calculation?</t>
+          <t>Positive electrolyte solute B chemical formula</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>K3Fe(CN)6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3077,27 +3075,27 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-rdfs:comment</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B molarity</t>
+          <t>Positive electrolyte solute B purity</t>
         </is>
       </c>
       <c r="B90" s="14" t="n">
-        <v>0.1</v>
+        <v>98</v>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -3108,19 +3106,19 @@
       <c r="E90" s="14" t="n"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B manufacturer</t>
+          <t>Positive electrolyte solute B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3133,25 +3131,29 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B manufacturer product ID</t>
+          <t>Positive electrolyte solute B molarity</t>
         </is>
       </c>
       <c r="B92" s="14" t="n">
-        <v>10266370</v>
+        <v>0.1</v>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -3162,130 +3164,130 @@
       <c r="E92" s="14" t="n"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive electrolyte volume  </t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="n">
-        <v>30</v>
+          <t>Positive electrolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Volume</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte volume flow rate</t>
+          <t>Positive electrolyte solute B manufacturer product ID</t>
         </is>
       </c>
       <c r="B94" s="14" t="n">
-        <v>60</v>
+        <v>10266370</v>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E94" s="14" t="n"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte volume flow rate calibration</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Flow calibrated with cell in series</t>
-        </is>
+          <t xml:space="preserve">Positive electrolyte volume  </t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>Comment if calibrated differently</t>
-        </is>
-      </c>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
+          <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte pressure</t>
-        </is>
-      </c>
-      <c r="B96" s="14" t="n"/>
+          <t>Positive electrolyte volume flow rate</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>60</v>
+      </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>mbar</t>
+          <t>mL/min</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E96" s="14" t="n"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
+          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte conductivity</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n">
-        <v>155.6</v>
+          <t>Positive electrolyte volume flow rate calibration</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Flow calibrated with cell in series</t>
+        </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3293,51 +3295,53 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E97" s="4" t="n"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Comment if calibrated differently</t>
+        </is>
+      </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasCatholyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte viscosity</t>
-        </is>
-      </c>
-      <c r="B98" s="14" t="n">
-        <v>1.34</v>
-      </c>
+          <t>Positive electrolyte pressure</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n"/>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>mPa·s</t>
+          <t>mbar</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E98" s="14" t="n"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-DynamicViscosity</t>
+          <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte pH</t>
+          <t>Positive electrolyte conductivity</t>
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>7.7</v>
+        <v>155.6</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3348,22 +3352,22 @@
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-PH</t>
+          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte density</t>
+          <t>Positive electrolyte viscosity</t>
         </is>
       </c>
       <c r="B100" s="14" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>g/cm3</t>
+          <t>mPa·s</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -3374,22 +3378,22 @@
       <c r="E100" s="14" t="n"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Density</t>
+          <t>hasCatholyte-hasMeasuredProperty-DynamicViscosity</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte temperature</t>
+          <t>Positive electrolyte pH</t>
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>23</v>
+        <v>7.7</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3400,22 +3404,22 @@
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
+          <t>hasCatholyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte tank volume</t>
+          <t>Positive electrolyte density</t>
         </is>
       </c>
       <c r="B102" s="14" t="n">
-        <v>50</v>
+        <v>1.13</v>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>g/cm3</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -3426,24 +3430,22 @@
       <c r="E102" s="14" t="n"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>hasComponent-type|CatholyteTank-hasMeasuredProperty-Volume</t>
+          <t>hasCatholyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte tank convection?</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Positive electrolyte temperature</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n">
+        <v>23</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3451,27 +3453,25 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|CatholyteTank-rdfs:comment</t>
+          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte gas</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="n"/>
+          <t>Positive electrolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -3479,27 +3479,27 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>Bubbled with Argon, Nitrogen, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E104" s="14" t="n"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasConstituent</t>
+          <t>hasComponent-type|CatholyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte gas flow rate</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="n"/>
+          <t>Positive electrolyte tank convection?</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3507,114 +3507,114 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n"/>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
+        </is>
+      </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasComponent-type|CatholyteTank-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte gas pressure</t>
+          <t>Positive electrolyte gas</t>
         </is>
       </c>
       <c r="B106" s="14" t="n"/>
       <c r="C106" s="14" t="inlineStr">
         <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>Bubbled with Argon, Nitrogen, leave empty if none</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasConstituent</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrolyte gas flow rate</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>Positive electrolyte gas pressure</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n"/>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
           <t>mbar</t>
         </is>
       </c>
-      <c r="D106" s="14" t="inlineStr">
+      <c r="D108" s="14" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E106" s="14" t="n"/>
-      <c r="F106" s="14" t="inlineStr">
+      <c r="E108" s="14" t="n"/>
+      <c r="F108" s="14" t="inlineStr">
         <is>
           <t>hasCatholyte-hasConstituent-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
         <is>
           <t>Negative electrolyte / negolyte / anolyte</t>
         </is>
       </c>
-      <c r="B107" s="16" t="n"/>
-      <c r="C107" s="16" t="n"/>
-      <c r="D107" s="16" t="n"/>
-      <c r="E107" s="16" t="n"/>
-      <c r="F107" s="16" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="17" t="inlineStr">
-        <is>
-          <t>Negative electrolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B109" s="17" t="inlineStr">
-        <is>
-          <t>Negolyte 1M</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E109" s="17" t="n"/>
-      <c r="F109" s="17" t="inlineStr">
-        <is>
-          <t>hasAnolyte-schema:productID</t>
-        </is>
-      </c>
+      <c r="B109" s="16" t="n"/>
+      <c r="C109" s="16" t="n"/>
+      <c r="D109" s="16" t="n"/>
+      <c r="E109" s="16" t="n"/>
+      <c r="F109" s="16" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A class</t>
+          <t>Negative electrolyte manufacturer</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -3627,26 +3627,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
+          <t>hasAnolyte-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A chemical name</t>
+          <t>Negative electrolyte manufacturer product ID</t>
         </is>
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Negolyte 1M</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
@@ -3656,29 +3652,25 @@
       </c>
       <c r="D111" s="17" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E111" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="n"/>
       <c r="F111" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A chemical formula</t>
+          <t>Negative electrolyte solvent A class</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>H2O</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -3693,50 +3685,56 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A purity</t>
-        </is>
-      </c>
-      <c r="B113" s="17" t="n">
-        <v>100</v>
+          <t>Negative electrolyte solvent A chemical name</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D113" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E113" s="17" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F113" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A purity considered in calculation?</t>
+          <t>Negative electrolyte solvent A chemical formula</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>H2O</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -3746,24 +3744,24 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-rdfs:comment</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A volume fraction</t>
+          <t>Negative electrolyte solvent A purity</t>
         </is>
       </c>
       <c r="B115" s="17" t="n">
@@ -3776,25 +3774,25 @@
       </c>
       <c r="D115" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E115" s="17" t="n"/>
       <c r="F115" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A manufacturer</t>
+          <t>Negative electrolyte solvent A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -3807,48 +3805,54 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E116" s="4" t="n"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B117" s="17" t="inlineStr">
-        <is>
-          <t>MilliQ</t>
-        </is>
+          <t>Negative electrolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="n">
+        <v>100</v>
       </c>
       <c r="C117" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D117" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E117" s="17" t="n"/>
       <c r="F117" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B class</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="n"/>
+          <t>Negative electrolyte solvent A manufacturer</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -3856,27 +3860,27 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B chemical name</t>
-        </is>
-      </c>
-      <c r="B119" s="17" t="n"/>
+          <t>Negative electrolyte solvent A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>MilliQ</t>
+        </is>
+      </c>
       <c r="C119" s="17" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -3887,21 +3891,17 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E119" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E119" s="17" t="n"/>
       <c r="F119" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B chemical formula</t>
+          <t>Negative electrolyte solvent B class</t>
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
@@ -3917,25 +3917,25 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B purity</t>
+          <t>Negative electrolyte solvent B chemical name</t>
         </is>
       </c>
       <c r="B121" s="17" t="n"/>
       <c r="C121" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D121" s="17" t="inlineStr">
@@ -3943,17 +3943,21 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E121" s="17" t="n"/>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F121" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B purity considered in calculation?</t>
+          <t>Negative electrolyte solvent B chemical formula</t>
         </is>
       </c>
       <c r="B122" s="4" t="n"/>
@@ -3969,24 +3973,22 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B123" s="17" t="n">
-        <v>0</v>
-      </c>
+          <t>Negative electrolyte solvent B purity</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="n"/>
       <c r="C123" s="17" t="inlineStr">
         <is>
           <t>%</t>
@@ -3994,20 +3996,20 @@
       </c>
       <c r="D123" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E123" s="17" t="n"/>
       <c r="F123" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B manufacturer</t>
+          <t>Negative electrolyte solvent B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B124" s="4" t="n"/>
@@ -4021,48 +4023,50 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E124" s="4" t="n"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B125" s="17" t="n"/>
+          <t>Negative electrolyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D125" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E125" s="17" t="n"/>
       <c r="F125" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A class</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
+          <t>Negative electrolyte solvent B manufacturer</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n"/>
       <c r="C126" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -4070,31 +4074,23 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A chemical name</t>
-        </is>
-      </c>
-      <c r="B127" s="17" t="inlineStr">
-        <is>
-          <t>KCrPDTA * 2 H2O (potassium [1,3-propylenediaminetetraacetato]chromate(III) dihydrate)</t>
-        </is>
-      </c>
+          <t>Negative electrolyte solvent B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="n"/>
       <c r="C127" s="17" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -4102,29 +4098,25 @@
       </c>
       <c r="D127" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E127" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E127" s="17" t="n"/>
       <c r="F127" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A chemical formula</t>
+          <t>Negative electrolyte solute A class</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>KCrC11H18N2O10</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -4134,32 +4126,34 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A purity</t>
-        </is>
-      </c>
-      <c r="B129" s="17" t="n">
-        <v>99</v>
+          <t>Negative electrolyte solute A chemical name</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>KCrPDTA * 2 H2O (potassium [1,3-propylenediaminetetraacetato]chromate(III) dihydrate)</t>
+        </is>
       </c>
       <c r="C129" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D129" s="17" t="inlineStr">
@@ -4167,22 +4161,26 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E129" s="17" t="n"/>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F129" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A purity considered in calculation?</t>
+          <t>Negative electrolyte solute A chemical formula</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>KCrC11H18N2O10</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -4197,50 +4195,50 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-rdfs:comment</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative electrolyte solute A molarity </t>
+          <t>Negative electrolyte solute A purity</t>
         </is>
       </c>
       <c r="B131" s="17" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="C131" s="17" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D131" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E131" s="17" t="n"/>
       <c r="F131" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A manufacturer</t>
+          <t>Negative electrolyte solute A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -4253,50 +4251,52 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E132" s="4" t="n"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A manufacturer productD</t>
-        </is>
-      </c>
-      <c r="B133" s="17" t="inlineStr">
-        <is>
-          <t>KCrPDTA-Fall-25</t>
-        </is>
+          <t xml:space="preserve">Negative electrolyte solute A molarity </t>
+        </is>
+      </c>
+      <c r="B133" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="C133" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D133" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E133" s="17" t="n"/>
       <c r="F133" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B class</t>
+          <t>Negative electrolyte solute A manufacturer</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>OrganicAcid</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -4306,29 +4306,25 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B chemical name</t>
+          <t>Negative electrolyte solute A manufacturer productD</t>
         </is>
       </c>
       <c r="B135" s="17" t="inlineStr">
         <is>
-          <t>H4PDTA (1,3-propylenediaminetetraacetic acid)</t>
+          <t>KCrPDTA-Fall-25</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
@@ -4338,29 +4334,25 @@
       </c>
       <c r="D135" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E135" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E135" s="17" t="n"/>
       <c r="F135" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B chemical formula</t>
+          <t>Negative electrolyte solute B class</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>C11H18N2O8</t>
+          <t>OrganicAcid</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -4375,27 +4367,29 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B purity</t>
-        </is>
-      </c>
-      <c r="B137" s="17" t="n">
-        <v>99</v>
+          <t>Negative electrolyte solute B chemical name</t>
+        </is>
+      </c>
+      <c r="B137" s="17" t="inlineStr">
+        <is>
+          <t>H4PDTA (1,3-propylenediaminetetraacetic acid)</t>
+        </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D137" s="17" t="inlineStr">
@@ -4403,22 +4397,26 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E137" s="17" t="n"/>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F137" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B purity considered in calculation?</t>
+          <t>Negative electrolyte solute B chemical formula</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>C11H18N2O8</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -4433,27 +4431,27 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-rdfs:comment</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B molarity</t>
+          <t>Negative electrolyte solute B purity</t>
         </is>
       </c>
       <c r="B139" s="17" t="n">
-        <v>0.1</v>
+        <v>99</v>
       </c>
       <c r="C139" s="17" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D139" s="17" t="inlineStr">
@@ -4464,19 +4462,19 @@
       <c r="E139" s="17" t="n"/>
       <c r="F139" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B manufacturer</t>
+          <t>Negative electrolyte solute B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>SigmaAldrich</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -4489,25 +4487,29 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E140" s="4" t="n"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B manufacturer product ID</t>
+          <t>Negative electrolyte solute B molarity</t>
         </is>
       </c>
       <c r="B141" s="17" t="n">
-        <v>33267</v>
+        <v>0.1</v>
       </c>
       <c r="C141" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D141" s="17" t="inlineStr">
@@ -4518,130 +4520,130 @@
       <c r="E141" s="17" t="n"/>
       <c r="F141" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative electrolyte volume  </t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="n">
-        <v>10</v>
+          <t>Negative electrolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>SigmaAldrich</t>
+        </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Volume</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte volume flow rate</t>
+          <t>Negative electrolyte solute B manufacturer product ID</t>
         </is>
       </c>
       <c r="B143" s="17" t="n">
-        <v>60</v>
+        <v>33267</v>
       </c>
       <c r="C143" s="17" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D143" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E143" s="17" t="n"/>
       <c r="F143" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte volume flow rate calibration</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>Flow calibrated with cell in series</t>
-        </is>
+          <t xml:space="preserve">Negative electrolyte volume  </t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>Comment if calibrated differently</t>
-        </is>
-      </c>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
+          <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte pressure</t>
-        </is>
-      </c>
-      <c r="B145" s="17" t="n"/>
+          <t>Negative electrolyte volume flow rate</t>
+        </is>
+      </c>
+      <c r="B145" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="C145" s="17" t="inlineStr">
         <is>
-          <t>mbar</t>
+          <t>mL/min</t>
         </is>
       </c>
       <c r="D145" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E145" s="17" t="n"/>
       <c r="F145" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
+          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte conductivity</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="n">
-        <v>48.4</v>
+          <t>Negative electrolyte volume flow rate calibration</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Flow calibrated with cell in series</t>
+        </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4649,51 +4651,53 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E146" s="4" t="n"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Comment if calibrated differently</t>
+        </is>
+      </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasAnolyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte viscosity</t>
-        </is>
-      </c>
-      <c r="B147" s="17" t="n">
-        <v>2.32</v>
-      </c>
+          <t>Negative electrolyte pressure</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="n"/>
       <c r="C147" s="17" t="inlineStr">
         <is>
-          <t>mPa·s</t>
+          <t>mbar</t>
         </is>
       </c>
       <c r="D147" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E147" s="17" t="n"/>
       <c r="F147" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-DynamicViscosity</t>
+          <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte pH</t>
+          <t>Negative electrolyte conductivity</t>
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4704,22 +4708,22 @@
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-PH</t>
+          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte density</t>
+          <t>Negative electrolyte viscosity</t>
         </is>
       </c>
       <c r="B149" s="17" t="n">
-        <v>1.21</v>
+        <v>2.32</v>
       </c>
       <c r="C149" s="17" t="inlineStr">
         <is>
-          <t>g/cm3</t>
+          <t>mPa·s</t>
         </is>
       </c>
       <c r="D149" s="17" t="inlineStr">
@@ -4730,22 +4734,22 @@
       <c r="E149" s="17" t="n"/>
       <c r="F149" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Density</t>
+          <t>hasAnolyte-hasMeasuredProperty-DynamicViscosity</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte temperature</t>
+          <t>Negative electrolyte pH</t>
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>23</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4756,22 +4760,22 @@
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
+          <t>hasAnolyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte tank volume</t>
+          <t>Negative electrolyte density</t>
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>50</v>
+        <v>1.21</v>
       </c>
       <c r="C151" s="17" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>g/cm3</t>
         </is>
       </c>
       <c r="D151" s="17" t="inlineStr">
@@ -4782,24 +4786,22 @@
       <c r="E151" s="17" t="n"/>
       <c r="F151" s="17" t="inlineStr">
         <is>
-          <t>hasComponent-type|AnolyteTank-hasMeasuredProperty-Volume</t>
+          <t>hasAnolyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte tank convection?</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>Bubbled with gas</t>
-        </is>
+          <t>Negative electrolyte temperature</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="n">
+        <v>23</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4807,31 +4809,25 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|AnolyteTank-rdfs:comment</t>
+          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte gas</t>
-        </is>
-      </c>
-      <c r="B153" s="17" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
+          <t>Negative electrolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B153" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="C153" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D153" s="17" t="inlineStr">
@@ -4839,29 +4835,27 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E153" s="17" t="inlineStr">
-        <is>
-          <t>e.g. Argon, Nitrogen, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E153" s="17" t="n"/>
       <c r="F153" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasConstituent</t>
+          <t>hasComponent-type|AnolyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte gas flow rate</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="n">
-        <v>2.5</v>
+          <t>Negative electrolyte tank convection?</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Bubbled with gas</t>
+        </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4869,120 +4863,122 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E154" s="4" t="n"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
+        </is>
+      </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasComponent-type|AnolyteTank-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="17" t="inlineStr">
         <is>
+          <t>Negative electrolyte gas</t>
+        </is>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E155" s="17" t="inlineStr">
+        <is>
+          <t>e.g. Argon, Nitrogen, leave empty if none</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasConstituent</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrolyte gas flow rate</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="inlineStr">
+        <is>
           <t>Negative electrolyte gas pressure</t>
         </is>
       </c>
-      <c r="B155" s="17" t="n">
+      <c r="B157" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="C155" s="17" t="inlineStr">
+      <c r="C157" s="17" t="inlineStr">
         <is>
           <t>mbar</t>
         </is>
       </c>
-      <c r="D155" s="17" t="inlineStr">
+      <c r="D157" s="17" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E155" s="17" t="n"/>
-      <c r="F155" s="17" t="inlineStr">
+      <c r="E157" s="17" t="n"/>
+      <c r="F157" s="17" t="inlineStr">
         <is>
           <t>hasAnolyte-hasConstituent-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="18" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
         <is>
           <t>Membrane</t>
         </is>
       </c>
-      <c r="B156" s="19" t="n"/>
-      <c r="C156" s="19" t="n"/>
-      <c r="D156" s="19" t="n"/>
-      <c r="E156" s="19" t="n"/>
-      <c r="F156" s="19" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>Membrane type</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane, AnionExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20" t="inlineStr">
-        <is>
-          <t>Membrane A manufacturer</t>
-        </is>
-      </c>
-      <c r="B158" s="20" t="inlineStr">
-        <is>
-          <t>Fumatech</t>
-        </is>
-      </c>
-      <c r="C158" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D158" s="20" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E158" s="20" t="n"/>
-      <c r="F158" s="20" t="inlineStr">
-        <is>
-          <t>hasSeparator-schema:manufacturer</t>
-        </is>
-      </c>
+      <c r="B158" s="19" t="n"/>
+      <c r="C158" s="19" t="n"/>
+      <c r="D158" s="19" t="n"/>
+      <c r="E158" s="19" t="n"/>
+      <c r="F158" s="19" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Membrane A manufacturer product ID</t>
+          <t>Membrane type</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>E630-K</t>
+          <t>CationExchangeMembrane</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4992,25 +4988,29 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane, AnionExchangeMembrane</t>
+        </is>
+      </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-schema:productID</t>
+          <t>hasSeparator</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>Membrane material A class</t>
+          <t>Membrane A manufacturer</t>
         </is>
       </c>
       <c r="B160" s="20" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>Fumatech</t>
         </is>
       </c>
       <c r="C160" s="20" t="inlineStr">
@@ -5023,26 +5023,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E160" s="20" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E160" s="20" t="n"/>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentA</t>
+          <t>hasSeparator-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Membrane material A chemical name</t>
+          <t>Membrane A manufacturer product ID</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Polyether ether ketone (PEEK)</t>
+          <t>E630-K</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -5055,26 +5051,22 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E161" s="4" t="n"/>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasSeparator-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>Membrane material A chemical formula</t>
+          <t>Membrane material A class</t>
         </is>
       </c>
       <c r="B162" s="20" t="inlineStr">
         <is>
-          <t>(C19H12O3)n</t>
+          <t>PolyetherEtherKetone</t>
         </is>
       </c>
       <c r="C162" s="20" t="inlineStr">
@@ -5084,27 +5076,31 @@
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E162" s="20" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasSeparator-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Membrane material B class</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="n"/>
+          <t>Membrane material A chemical name</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Polyether ether ketone (PEEK)</t>
+        </is>
+      </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5112,27 +5108,31 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Ontology term, be as specific as possible</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentB</t>
+          <t>hasSeparator-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>Membrane material B chemical name</t>
-        </is>
-      </c>
-      <c r="B164" s="20" t="n"/>
+          <t>Membrane material A chemical formula</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="inlineStr">
+        <is>
+          <t>(C19H12O3)n</t>
+        </is>
+      </c>
       <c r="C164" s="20" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E164" s="20" t="inlineStr">
@@ -5150,14 +5150,14 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasSeparator-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Membrane material B chemical formula</t>
+          <t>Membrane material B class</t>
         </is>
       </c>
       <c r="B165" s="4" t="n"/>
@@ -5173,77 +5173,83 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasSeparator-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>Membrane thickness</t>
-        </is>
-      </c>
-      <c r="B166" s="20" t="n">
-        <v>30</v>
-      </c>
+          <t>Membrane material B chemical name</t>
+        </is>
+      </c>
+      <c r="B166" s="20" t="n"/>
       <c r="C166" s="20" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E166" s="20" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F166" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-Thickness</t>
+          <t>hasSeparator-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Membrane area specific conductivity</t>
+          <t>Membrane material B chemical formula</t>
         </is>
       </c>
       <c r="B167" s="4" t="n"/>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasSeparator-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>Membrane projected area</t>
+          <t>Membrane thickness</t>
         </is>
       </c>
       <c r="B168" s="20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C168" s="20" t="inlineStr">
         <is>
-          <t>cm2</t>
+          <t>um</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
@@ -5254,24 +5260,20 @@
       <c r="E168" s="20" t="n"/>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-Area</t>
+          <t>hasSeparator-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane storage </t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>Water, &gt;24 h, room temperature</t>
-        </is>
-      </c>
+          <t>Membrane area specific conductivity</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="n"/>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5279,130 +5281,124 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>Describe membrane storage conditions (medium, duration, temperature)</t>
-        </is>
-      </c>
+      <c r="E169" s="4" t="n"/>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-rdfs:comment</t>
+          <t>hasSeparator-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
+          <t>Membrane projected area</t>
+        </is>
+      </c>
+      <c r="B170" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E170" s="20" t="n"/>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasMeasuredProperty-Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Membrane storage </t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Water, &gt;24 h, room temperature</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Describe membrane storage conditions (medium, duration, temperature)</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Membrane pre-treatment </t>
         </is>
       </c>
-      <c r="B170" s="20" t="inlineStr">
+      <c r="B172" s="20" t="inlineStr">
         <is>
           <t>Untreated membrane</t>
         </is>
       </c>
-      <c r="C170" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D170" s="20" t="inlineStr">
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E170" s="20" t="inlineStr">
+      <c r="E172" s="20" t="inlineStr">
         <is>
           <t>Describe membrane pre-treatment conditions (medium, duration, temperature)</t>
         </is>
       </c>
-      <c r="F170" s="20" t="inlineStr">
+      <c r="F172" s="20" t="inlineStr">
         <is>
           <t>hasSeparator-rdfs:comment</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Cell assembly</t>
         </is>
       </c>
-      <c r="B171" s="3" t="n"/>
-      <c r="C171" s="3" t="n"/>
-      <c r="D171" s="3" t="n"/>
-      <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>Cell case type</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>FlowCell</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>hasCase</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Cell case manufacturer</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>Fuel Cell Technologies</t>
-        </is>
-      </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>Fuel Cell Technologies, Pinflow, etc.</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>hasCase-schema:manufacturer</t>
-        </is>
-      </c>
+      <c r="B173" s="3" t="n"/>
+      <c r="C173" s="3" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Cell case manufacturer product ID</t>
+          <t>Cell case type</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>5SCH</t>
+          <t>FlowCell</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -5412,25 +5408,25 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>hasCase-schema:productID</t>
+          <t>hasCase</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Flowfield material class</t>
+          <t>Cell case manufacturer</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Fuel Cell Technologies</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -5445,24 +5441,24 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Ontology term, be as specific as possible</t>
+          <t>Fuel Cell Technologies, Pinflow, etc.</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField</t>
+          <t>hasCase-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Flowfield material chemical name</t>
+          <t>Cell case manufacturer product ID</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>5SCH</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -5472,29 +5468,25 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n"/>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCase-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Flowfield material chemical formula</t>
+          <t>Flowfield material class</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -5509,24 +5501,24 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasComponent-type|FlowField</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Flowfield type</t>
+          <t>Flowfield material chemical name</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -5539,22 +5531,26 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E178" s="4" t="n"/>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-schema:description</t>
+          <t>hasComponent-type|FlowField-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Flowfield manufacturer</t>
+          <t>Flowfield material chemical formula</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -5567,22 +5563,26 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n"/>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-schema:manufacturer</t>
+          <t>hasComponent-type|FlowField-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Flowfield manufacturer product ID</t>
+          <t>Flowfield type</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>5SCH-PB</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-schema:productID</t>
+          <t>hasComponent-type|FlowField-schema:description</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Gasket material class</t>
+          <t>Flowfield manufacturer</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>PolymerCompound</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -5623,26 +5623,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E181" s="5" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E181" s="5" t="n"/>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket</t>
+          <t>hasComponent-type|FlowField-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Gasket material chemical name</t>
+          <t>Flowfield manufacturer product ID</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Viton</t>
+          <t>5SCH-PB</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -5655,24 +5651,24 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E182" s="4" t="n"/>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasComponent-type|FlowField-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Gasket material chemical formula</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="n"/>
+          <t>Gasket material class</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>PolymerCompound</t>
+        </is>
+      </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5680,29 +5676,29 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasComponent-type|Gasket</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Gasket manufacturer</t>
+          <t>Gasket material chemical name</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Maagtechnic AG</t>
+          <t>Viton</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -5715,22 +5711,24 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E184" s="4" t="n"/>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-schema:manufacturer</t>
+          <t>hasComponent-type|Gasket-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Gasket manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="n">
-        <v>17965343</v>
-      </c>
+          <t>Gasket material chemical formula</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="n"/>
       <c r="C185" s="5" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5741,51 +5739,57 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E185" s="5" t="n"/>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-schema:productID</t>
+          <t>hasComponent-type|Gasket-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Gasket thickness</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="n">
-        <v>450</v>
+          <t>Gasket manufacturer</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Maagtechnic AG</t>
+        </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-hasMeasuredProperty-Thickness</t>
+          <t>hasComponent-type|Gasket-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Torque upon assembly</t>
+          <t>Gasket manufacturer product ID</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
-        <v>6</v>
+        <v>17965343</v>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Nm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
@@ -5796,24 +5800,22 @@
       <c r="E187" s="5" t="n"/>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>hasCase-hasMeasuredProperty-Torque</t>
+          <t>hasComponent-type|Gasket-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>Connector type</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>Banana plug connected via crocodile clamp</t>
-        </is>
+          <t>Gasket thickness</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="n">
+        <v>450</v>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>um</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5821,31 +5823,25 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>Describe cell lead-instrument connection</t>
-        </is>
-      </c>
+      <c r="E188" s="4" t="n"/>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|Connector-rdfs:comment</t>
+          <t>hasComponent-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Connection type</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
-        <is>
-          <t>4-point</t>
-        </is>
+          <t>Torque upon assembly</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>Nm</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
@@ -5853,42 +5849,102 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
-        <is>
-          <t>Describe if other mode, e.g. 2-point</t>
-        </is>
-      </c>
+      <c r="E189" s="5" t="n"/>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Connector-rdfs:comment</t>
+          <t>hasCase-hasMeasuredProperty-Torque</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
+          <t>Connector type</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Banana plug connected via crocodile clamp</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Describe cell lead-instrument connection</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>hasComponent-type|Connector-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>Connection type</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>4-point</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>Describe if other mode, e.g. 2-point</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>hasComponent-type|Connector-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
           <t>Assembled resistance</t>
         </is>
       </c>
-      <c r="B190" s="4" t="n">
+      <c r="B192" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="C190" s="4" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
         <is>
           <t>ohm</t>
         </is>
       </c>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>Resistance of the as-assembled cell, before any experiments</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>hasMeasuredProperty-ElectricResistance</t>
         </is>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -2911,7 +2911,7 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive electrolyte solute A molarity </t>
+          <t>Positive electrolyte solute A molarity</t>
         </is>
       </c>
       <c r="B84" s="14" t="n">
@@ -3225,7 +3225,7 @@
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive electrolyte volume  </t>
+          <t>Positive electrolyte volume</t>
         </is>
       </c>
       <c r="B95" s="4" t="n">
@@ -4265,7 +4265,7 @@
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative electrolyte solute A molarity </t>
+          <t>Negative electrolyte solute A molarity</t>
         </is>
       </c>
       <c r="B133" s="17" t="n">
@@ -4581,7 +4581,7 @@
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative electrolyte volume  </t>
+          <t>Negative electrolyte volume</t>
         </is>
       </c>
       <c r="B144" s="4" t="n">
@@ -5317,7 +5317,7 @@
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane storage </t>
+          <t>Membrane storage</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
@@ -5349,7 +5349,7 @@
     <row r="172">
       <c r="A172" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane pre-treatment </t>
+          <t>Membrane pre-treatment</t>
         </is>
       </c>
       <c r="B172" s="20" t="inlineStr">

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -848,7 +848,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0.1.3</t>
+          <t>0.1.4</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate</t>
+          <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate</t>
+          <t>hasPositiveElectrode-hasSubstrate</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-schema:manufacturer</t>
+          <t>hasPositiveElectrode-hasSubstrate-schema:manufacturer</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-schema:productID</t>
+          <t>hasPositiveElectrode-hasSubstrate-schema:productID</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Thickness</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       <c r="E24" s="8" t="n"/>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Porosity</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Area</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Area</t>
         </is>
       </c>
     </row>
@@ -1284,22 +1284,24 @@
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Thickness</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode weight</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="n">
-        <v>53.2</v>
+          <t>Positive electrode substrate thickness in cell comment</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Thickness under compression</t>
+        </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>mg</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1310,51 +1312,45 @@
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-hasMeasuredProperty-Weight</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Positive electrode substrate treatment (Untreated, Chemical, Thermal)</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Untreated electrode</t>
-        </is>
+          <t>Positive electrode weight</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>53.2</v>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mg</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="n"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-Substrate-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material type</t>
+          <t>Positive electrode substrate treatment (Untreated, Chemical, Thermal)</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>Untreated electrode</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1364,25 +1360,29 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
+          <t>hasPositiveElectrode-hasSubstrate-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material class</t>
+          <t>Positive electrode coating active material type</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>TitaniumDioxide</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1395,11 +1395,7 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E30" s="8" t="n"/>
       <c r="F30" s="8" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
@@ -1409,12 +1405,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material chemical name</t>
+          <t>Positive electrode coating active material class</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Titanium dioxide</t>
+          <t>TitaniumDioxide</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1429,24 +1425,24 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material chemical formula</t>
+          <t>Positive electrode coating active material chemical name</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>TiO2</t>
+          <t>Titanium dioxide</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -1466,19 +1462,19 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Positive electrode coating active material description</t>
+          <t>Positive electrode coating active material chemical formula</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Liquid-phase deposition using a mixed solution of H3BO3 and (NH4)2TiF6</t>
+          <t>TiO2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1493,774 +1489,778 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Describe catalyst deposition procedure</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode-hasCoating-rdfs:comment</t>
+          <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
+          <t>Positive electrode coating active material description</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Liquid-phase deposition using a mixed solution of H3BO3 and (NH4)2TiF6</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Describe catalyst deposition procedure</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>hasPositiveElectrode-hasCoating-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>Positive electrode coating active material mass loading</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n">
+      <c r="B35" s="4" t="n">
         <v>1.3579</v>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>mg/cm2</t>
         </is>
       </c>
-      <c r="D34" s="8" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>hasPositiveElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Negative electrode</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="10" t="n"/>
-      <c r="F35" s="10" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Negative electrode type</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>PorousElectrode</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:manufacturer</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Negative electrode manufacturer product ID</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Pristine</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E38" s="4" t="n"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-schema:productID</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate type</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E39" s="11" t="inlineStr">
+      <c r="E40" s="11" t="inlineStr">
         <is>
           <t>CarbonPaper, CarbonFelt, CarbonCloth etc.</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate material class</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate material chemical name</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasDatumA-type|ChemicalName-hasStringValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasDatumA-type|ChemicalName-hasStringValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate material chemical formula</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate manufacturer</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>SGL Carbon</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-schema:manufacturer</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate product ID</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Sigracet 39AA</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-schema:productID</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-schema:productID</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate thickness</t>
         </is>
       </c>
-      <c r="B45" s="11" t="n">
+      <c r="B46" s="11" t="n">
         <v>560</v>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C46" s="11" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D46" s="11" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate thickness comment</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Used two 280 µm carbon papers</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Describe stacking of multiple electrode components or if single elctrode was used</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-rdfs:comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Negative electrode substrate porosity</t>
         </is>
       </c>
-      <c r="B47" s="11" t="n">
+      <c r="B48" s="11" t="n">
         <v>80</v>
       </c>
-      <c r="C47" s="11" t="inlineStr">
+      <c r="C48" s="11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D48" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Porosity</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Negative electrode geometric area</t>
         </is>
       </c>
-      <c r="B48" s="4" t="n">
+      <c r="B49" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>cm2</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Area</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>Negative electrode thickness in cell (including compression)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B50" s="11" t="n">
         <v>450</v>
       </c>
-      <c r="C49" s="11" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>um</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D50" s="11" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Thickness</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="E50" s="11" t="n"/>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Thickness</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrode substrate thickness in cell comment</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Thickness under compression</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-type|Thickness-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>Negative electrode weight</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n">
+      <c r="B52" s="11" t="n">
         <v>52.3</v>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D52" s="11" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-hasMeasuredProperty-Weight</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="11" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-hasMeasuredProperty-Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Negative electrode substrate treatment (Untreated, Chemical, Thermal)</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Untreated electrode</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>required</t>
         </is>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Describe treatment conditions (temperature, heat/cool rate, atmosphere, dwell time, etc.)</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-Substrate-rdfs:comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>hasNegativeElectrode-hasSubstrate-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
         <is>
           <t>Negative electrode coating active material type</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Negative electrode coating active material class</t>
         </is>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C53" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E53" s="11" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
         <is>
           <t>Negative electrode coating active material chemical name</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E56" s="11" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F56" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Negative electrode coating active material chemical formula</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Bi</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E55" s="11" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>Important if specific ontology class not available</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>Negative electrode coating active material description</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>Deposited from BiCl3 solution</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>Describe catalyst deposition procedure</t>
         </is>
       </c>
-      <c r="F56" s="4" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>hasNegativeElectrode-hasCoating-rdfs:comment</t>
         </is>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Negative electrode coating active material mass loading</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>1.23456</v>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>mg/cm2</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E57" s="11" t="n"/>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
-        <is>
-          <t>Positive electrolyte / posolyte / catholyte</t>
-        </is>
-      </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
+          <t>Negative electrode coating active material mass loading</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>1.23456</v>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mg/cm2</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-schema:manufacturer</t>
+          <t>hasNegativeElectrode-hasCoating-hasActiveMaterial-hasMeasuredProperty-MassLoading</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Positive electrolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Posolyte 0.5M</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D60" s="14" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="n"/>
-      <c r="F60" s="14" t="inlineStr">
-        <is>
-          <t>hasCatholyte-schema:productID</t>
-        </is>
-      </c>
+      <c r="A60" s="12" t="inlineStr">
+        <is>
+          <t>Positive electrolyte / posolyte / catholyte</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A class</t>
+          <t>Positive electrolyte manufacturer</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -2273,26 +2273,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
+          <t>hasCatholyte-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A chemical name</t>
+          <t>Positive electrolyte manufacturer product ID</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Posolyte 0.5M</t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
@@ -2302,29 +2298,25 @@
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E62" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="n"/>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A chemical formula</t>
+          <t>Positive electrolyte solvent A class</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>H2O</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2339,50 +2331,56 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A purity</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="n">
-        <v>100</v>
+          <t>Positive electrolyte solvent A chemical name</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E64" s="14" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E64" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A purity considered in calculation?</t>
+          <t>Positive electrolyte solvent A chemical formula</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>H2O</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2392,24 +2390,24 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-rdfs:comment</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A volume fraction</t>
+          <t>Positive electrolyte solvent A purity</t>
         </is>
       </c>
       <c r="B66" s="14" t="n">
@@ -2422,25 +2420,25 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E66" s="14" t="n"/>
       <c r="F66" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A manufacturer</t>
+          <t>Positive electrolyte solvent A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -2453,48 +2451,54 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E67" s="4" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>MilliQ</t>
-        </is>
+          <t>Positive electrolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="n">
+        <v>100</v>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E68" s="14" t="n"/>
       <c r="F68" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B class</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n"/>
+          <t>Positive electrolyte solvent A manufacturer</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2502,27 +2506,27 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B chemical name</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="n"/>
+          <t>Positive electrolyte solvent A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>MilliQ</t>
+        </is>
+      </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2533,21 +2537,17 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E70" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E70" s="14" t="n"/>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B chemical formula</t>
+          <t>Positive electrolyte solvent B class</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B purity</t>
+          <t>Positive electrolyte solvent B chemical name</t>
         </is>
       </c>
       <c r="B72" s="14" t="n"/>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
@@ -2589,17 +2589,21 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E72" s="14" t="n"/>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F72" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B purity considered in calculation?</t>
+          <t>Positive electrolyte solvent B chemical formula</t>
         </is>
       </c>
       <c r="B73" s="4" t="n"/>
@@ -2615,24 +2619,22 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B74" s="14" t="n">
-        <v>0</v>
-      </c>
+          <t>Positive electrolyte solvent B purity</t>
+        </is>
+      </c>
+      <c r="B74" s="14" t="n"/>
       <c r="C74" s="14" t="inlineStr">
         <is>
           <t>%</t>
@@ -2640,20 +2642,20 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E74" s="14" t="n"/>
       <c r="F74" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B manufacturer</t>
+          <t>Positive electrolyte solvent B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
@@ -2667,48 +2669,50 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E75" s="4" t="n"/>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solvent B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="n"/>
+          <t>Positive electrolyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E76" s="14" t="n"/>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A class</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
+          <t>Positive electrolyte solvent B manufacturer</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
       <c r="C77" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2716,31 +2720,23 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A chemical name</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>Potassium ferrocyanide trihydrate</t>
-        </is>
-      </c>
+          <t>Positive electrolyte solvent B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="n"/>
       <c r="C78" s="14" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -2748,29 +2744,25 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E78" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E78" s="14" t="n"/>
       <c r="F78" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A chemical formula</t>
+          <t>Positive electrolyte solute A class</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>K4Fe(CN)6 * 3 H2O</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
@@ -2780,32 +2772,34 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A purity</t>
-        </is>
-      </c>
-      <c r="B80" s="14" t="n">
-        <v>99</v>
+          <t>Positive electrolyte solute A chemical name</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Potassium ferrocyanide trihydrate</t>
+        </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -2813,22 +2807,26 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E80" s="14" t="n"/>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A purity considered in calculation?</t>
+          <t>Positive electrolyte solute A chemical formula</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>K4Fe(CN)6 * 3 H2O</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -2843,50 +2841,50 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-rdfs:comment</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive electrolyte solute A molarity </t>
+          <t>Positive electrolyte solute A purity</t>
         </is>
       </c>
       <c r="B82" s="14" t="n">
-        <v>0.5</v>
+        <v>99</v>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E82" s="14" t="n"/>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A manufacturer</t>
+          <t>Positive electrolyte solute A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
@@ -2899,48 +2897,52 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E83" s="4" t="n"/>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute A manufacturer productD</t>
+          <t>Positive electrolyte solute A molarity</t>
         </is>
       </c>
       <c r="B84" s="14" t="n">
-        <v>10504474</v>
+        <v>0.5</v>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E84" s="14" t="n"/>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B class</t>
+          <t>Positive electrolyte solute A manufacturer</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>PotassiumSaltCompound</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
@@ -2950,30 +2952,24 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B chemical name</t>
-        </is>
-      </c>
-      <c r="B86" s="14" t="inlineStr">
-        <is>
-          <t>Potassium ferricyanide</t>
-        </is>
+          <t>Positive electrolyte solute A manufacturer productD</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="n">
+        <v>10504474</v>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
@@ -2982,29 +2978,25 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="n"/>
       <c r="F86" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCatholyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B chemical formula</t>
+          <t>Positive electrolyte solute B class</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>K3Fe(CN)6</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
@@ -3019,27 +3011,29 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B purity</t>
-        </is>
-      </c>
-      <c r="B88" s="14" t="n">
-        <v>98</v>
+          <t>Positive electrolyte solute B chemical name</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="inlineStr">
+        <is>
+          <t>Potassium ferricyanide</t>
+        </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
@@ -3047,22 +3041,26 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E88" s="14" t="n"/>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B purity considered in calculation?</t>
+          <t>Positive electrolyte solute B chemical formula</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>K3Fe(CN)6</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
@@ -3077,27 +3075,27 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-rdfs:comment</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B molarity</t>
+          <t>Positive electrolyte solute B purity</t>
         </is>
       </c>
       <c r="B90" s="14" t="n">
-        <v>0.1</v>
+        <v>98</v>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -3108,19 +3106,19 @@
       <c r="E90" s="14" t="n"/>
       <c r="F90" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B manufacturer</t>
+          <t>Positive electrolyte solute B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
@@ -3133,25 +3131,29 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E91" s="4" t="n"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte solute B manufacturer product ID</t>
+          <t>Positive electrolyte solute B molarity</t>
         </is>
       </c>
       <c r="B92" s="14" t="n">
-        <v>10266370</v>
+        <v>0.1</v>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -3162,130 +3164,130 @@
       <c r="E92" s="14" t="n"/>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Positive electrolyte volume  </t>
-        </is>
-      </c>
-      <c r="B93" s="4" t="n">
-        <v>30</v>
+          <t>Positive electrolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Volume</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte volume flow rate</t>
+          <t>Positive electrolyte solute B manufacturer product ID</t>
         </is>
       </c>
       <c r="B94" s="14" t="n">
-        <v>60</v>
+        <v>10266370</v>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E94" s="14" t="n"/>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasCatholyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte volume flow rate calibration</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Flow calibrated with cell in series</t>
-        </is>
+          <t>Positive electrolyte volume</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="n">
+        <v>30</v>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>Comment if calibrated differently</t>
-        </is>
-      </c>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate-rdfs:comment</t>
+          <t>hasCatholyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte pressure</t>
-        </is>
-      </c>
-      <c r="B96" s="14" t="n"/>
+          <t>Positive electrolyte volume flow rate</t>
+        </is>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>60</v>
+      </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>mbar</t>
+          <t>mL/min</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E96" s="14" t="n"/>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
+          <t>hasCatholyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte conductivity</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="n">
-        <v>155.6</v>
+          <t>Positive electrolyte volume flow rate calibration</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Flow calibrated with cell in series</t>
+        </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3293,51 +3295,53 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E97" s="4" t="n"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Comment if calibrated differently</t>
+        </is>
+      </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasCatholyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte viscosity</t>
-        </is>
-      </c>
-      <c r="B98" s="14" t="n">
-        <v>1.34</v>
-      </c>
+          <t>Positive electrolyte pressure</t>
+        </is>
+      </c>
+      <c r="B98" s="14" t="n"/>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>mPa·s</t>
+          <t>mbar</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E98" s="14" t="n"/>
       <c r="F98" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-DynamicViscosity</t>
+          <t>hasCatholyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte pH</t>
+          <t>Positive electrolyte conductivity</t>
         </is>
       </c>
       <c r="B99" s="4" t="n">
-        <v>7.7</v>
+        <v>155.6</v>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3348,22 +3352,22 @@
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-PH</t>
+          <t>hasCatholyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte density</t>
+          <t>Positive electrolyte viscosity</t>
         </is>
       </c>
       <c r="B100" s="14" t="n">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>g/cm3</t>
+          <t>mPa·s</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
@@ -3374,22 +3378,22 @@
       <c r="E100" s="14" t="n"/>
       <c r="F100" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-Density</t>
+          <t>hasCatholyte-hasMeasuredProperty-DynamicViscosity</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte temperature</t>
+          <t>Positive electrolyte pH</t>
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>23</v>
+        <v>7.7</v>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3400,22 +3404,22 @@
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
+          <t>hasCatholyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte tank volume</t>
+          <t>Positive electrolyte density</t>
         </is>
       </c>
       <c r="B102" s="14" t="n">
-        <v>50</v>
+        <v>1.13</v>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>g/cm3</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -3426,24 +3430,22 @@
       <c r="E102" s="14" t="n"/>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>hasComponent-type|CatholyteTank-hasMeasuredProperty-Volume</t>
+          <t>hasCatholyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte tank convection?</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+          <t>Positive electrolyte temperature</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="n">
+        <v>23</v>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3451,27 +3453,25 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|CatholyteTank-rdfs:comment</t>
+          <t>hasCatholyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte gas</t>
-        </is>
-      </c>
-      <c r="B104" s="14" t="n"/>
+          <t>Positive electrolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>50</v>
+      </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -3479,27 +3479,27 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E104" s="14" t="inlineStr">
-        <is>
-          <t>Bubbled with Argon, Nitrogen, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E104" s="14" t="n"/>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasConstituent</t>
+          <t>hasComponent-type|CatholyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Positive electrolyte gas flow rate</t>
-        </is>
-      </c>
-      <c r="B105" s="4" t="n"/>
+          <t>Positive electrolyte tank convection?</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3507,114 +3507,114 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E105" s="4" t="n"/>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
+        </is>
+      </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>hasCatholyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasComponent-type|CatholyteTank-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>Positive electrolyte gas pressure</t>
+          <t>Positive electrolyte gas</t>
         </is>
       </c>
       <c r="B106" s="14" t="n"/>
       <c r="C106" s="14" t="inlineStr">
         <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>Bubbled with Argon, Nitrogen, leave empty if none</t>
+        </is>
+      </c>
+      <c r="F106" s="14" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasConstituent</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Positive electrolyte gas flow rate</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>hasCatholyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>Positive electrolyte gas pressure</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n"/>
+      <c r="C108" s="14" t="inlineStr">
+        <is>
           <t>mbar</t>
         </is>
       </c>
-      <c r="D106" s="14" t="inlineStr">
+      <c r="D108" s="14" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E106" s="14" t="n"/>
-      <c r="F106" s="14" t="inlineStr">
+      <c r="E108" s="14" t="n"/>
+      <c r="F108" s="14" t="inlineStr">
         <is>
           <t>hasCatholyte-hasConstituent-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="15" t="inlineStr">
         <is>
           <t>Negative electrolyte / negolyte / anolyte</t>
         </is>
       </c>
-      <c r="B107" s="16" t="n"/>
-      <c r="C107" s="16" t="n"/>
-      <c r="D107" s="16" t="n"/>
-      <c r="E107" s="16" t="n"/>
-      <c r="F107" s="16" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="4" t="inlineStr">
-        <is>
-          <t>Negative electrolyte manufacturer</t>
-        </is>
-      </c>
-      <c r="B108" s="4" t="inlineStr">
-        <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="C108" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D108" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E108" s="4" t="n"/>
-      <c r="F108" s="4" t="inlineStr">
-        <is>
-          <t>hasAnolyte-schema:manufacturer</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="17" t="inlineStr">
-        <is>
-          <t>Negative electrolyte manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B109" s="17" t="inlineStr">
-        <is>
-          <t>Negolyte 1M</t>
-        </is>
-      </c>
-      <c r="C109" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D109" s="17" t="inlineStr">
-        <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E109" s="17" t="n"/>
-      <c r="F109" s="17" t="inlineStr">
-        <is>
-          <t>hasAnolyte-schema:productID</t>
-        </is>
-      </c>
+      <c r="B109" s="16" t="n"/>
+      <c r="C109" s="16" t="n"/>
+      <c r="D109" s="16" t="n"/>
+      <c r="E109" s="16" t="n"/>
+      <c r="F109" s="16" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A class</t>
+          <t>Negative electrolyte manufacturer</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
@@ -3627,26 +3627,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E110" s="4" t="n"/>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
+          <t>hasAnolyte-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A chemical name</t>
+          <t>Negative electrolyte manufacturer product ID</t>
         </is>
       </c>
       <c r="B111" s="17" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Negolyte 1M</t>
         </is>
       </c>
       <c r="C111" s="17" t="inlineStr">
@@ -3656,29 +3652,25 @@
       </c>
       <c r="D111" s="17" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E111" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E111" s="17" t="n"/>
       <c r="F111" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A chemical formula</t>
+          <t>Negative electrolyte solvent A class</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>H2O</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
@@ -3693,50 +3685,56 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A purity</t>
-        </is>
-      </c>
-      <c r="B113" s="17" t="n">
-        <v>100</v>
+          <t>Negative electrolyte solvent A chemical name</t>
+        </is>
+      </c>
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
       </c>
       <c r="C113" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D113" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E113" s="17" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F113" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A purity considered in calculation?</t>
+          <t>Negative electrolyte solvent A chemical formula</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>H2O</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -3746,24 +3744,24 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-rdfs:comment</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A volume fraction</t>
+          <t>Negative electrolyte solvent A purity</t>
         </is>
       </c>
       <c r="B115" s="17" t="n">
@@ -3776,25 +3774,25 @@
       </c>
       <c r="D115" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E115" s="17" t="n"/>
       <c r="F115" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A manufacturer</t>
+          <t>Negative electrolyte solvent A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -3807,48 +3805,54 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E116" s="4" t="n"/>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent A manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B117" s="17" t="inlineStr">
-        <is>
-          <t>MilliQ</t>
-        </is>
+          <t>Negative electrolyte solvent A volume fraction</t>
+        </is>
+      </c>
+      <c r="B117" s="17" t="n">
+        <v>100</v>
       </c>
       <c r="C117" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D117" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E117" s="17" t="n"/>
       <c r="F117" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B class</t>
-        </is>
-      </c>
-      <c r="B118" s="4" t="n"/>
+          <t>Negative electrolyte solvent A manufacturer</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -3856,27 +3860,27 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="n"/>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B chemical name</t>
-        </is>
-      </c>
-      <c r="B119" s="17" t="n"/>
+          <t>Negative electrolyte solvent A manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B119" s="17" t="inlineStr">
+        <is>
+          <t>MilliQ</t>
+        </is>
+      </c>
       <c r="C119" s="17" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -3887,21 +3891,17 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E119" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E119" s="17" t="n"/>
       <c r="F119" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B chemical formula</t>
+          <t>Negative electrolyte solvent B class</t>
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
@@ -3917,25 +3917,25 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B purity</t>
+          <t>Negative electrolyte solvent B chemical name</t>
         </is>
       </c>
       <c r="B121" s="17" t="n"/>
       <c r="C121" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D121" s="17" t="inlineStr">
@@ -3943,17 +3943,21 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E121" s="17" t="n"/>
+      <c r="E121" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F121" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B purity considered in calculation?</t>
+          <t>Negative electrolyte solvent B chemical formula</t>
         </is>
       </c>
       <c r="B122" s="4" t="n"/>
@@ -3969,24 +3973,22 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B volume fraction</t>
-        </is>
-      </c>
-      <c r="B123" s="17" t="n">
-        <v>0</v>
-      </c>
+          <t>Negative electrolyte solvent B purity</t>
+        </is>
+      </c>
+      <c r="B123" s="17" t="n"/>
       <c r="C123" s="17" t="inlineStr">
         <is>
           <t>%</t>
@@ -3994,20 +3996,20 @@
       </c>
       <c r="D123" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E123" s="17" t="n"/>
       <c r="F123" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B manufacturer</t>
+          <t>Negative electrolyte solvent B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B124" s="4" t="n"/>
@@ -4021,48 +4023,50 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E124" s="4" t="n"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solvent B manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B125" s="17" t="n"/>
+          <t>Negative electrolyte solvent B volume fraction</t>
+        </is>
+      </c>
+      <c r="B125" s="17" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D125" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E125" s="17" t="n"/>
       <c r="F125" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-hasMeasuredProperty-VolumeFraction</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A class</t>
-        </is>
-      </c>
-      <c r="B126" s="4" t="inlineStr">
-        <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
+          <t>Negative electrolyte solvent B manufacturer</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="n"/>
       <c r="C126" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -4070,31 +4074,23 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A chemical name</t>
-        </is>
-      </c>
-      <c r="B127" s="17" t="inlineStr">
-        <is>
-          <t>KCrPDTA * 2 H2O (potassium [1,3-propylenediaminetetraacetato]chromate(III) dihydrate)</t>
-        </is>
-      </c>
+          <t>Negative electrolyte solvent B manufacturer product ID</t>
+        </is>
+      </c>
+      <c r="B127" s="17" t="n"/>
       <c r="C127" s="17" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -4102,29 +4098,25 @@
       </c>
       <c r="D127" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E127" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E127" s="17" t="n"/>
       <c r="F127" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-hasSolvent-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A chemical formula</t>
+          <t>Negative electrolyte solute A class</t>
         </is>
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>KCrC11H18N2O10</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -4134,32 +4126,34 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A purity</t>
-        </is>
-      </c>
-      <c r="B129" s="17" t="n">
-        <v>99</v>
+          <t>Negative electrolyte solute A chemical name</t>
+        </is>
+      </c>
+      <c r="B129" s="17" t="inlineStr">
+        <is>
+          <t>KCrPDTA * 2 H2O (potassium [1,3-propylenediaminetetraacetato]chromate(III) dihydrate)</t>
+        </is>
       </c>
       <c r="C129" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D129" s="17" t="inlineStr">
@@ -4167,22 +4161,26 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E129" s="17" t="n"/>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F129" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A purity considered in calculation?</t>
+          <t>Negative electrolyte solute A chemical formula</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>KCrC11H18N2O10</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -4197,50 +4195,50 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-rdfs:comment</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative electrolyte solute A molarity </t>
+          <t>Negative electrolyte solute A purity</t>
         </is>
       </c>
       <c r="B131" s="17" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="C131" s="17" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D131" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E131" s="17" t="n"/>
       <c r="F131" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A manufacturer</t>
+          <t>Negative electrolyte solute A purity considered in calculation?</t>
         </is>
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -4253,50 +4251,52 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E132" s="4" t="n"/>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute A manufacturer productD</t>
-        </is>
-      </c>
-      <c r="B133" s="17" t="inlineStr">
-        <is>
-          <t>KCrPDTA-Fall-25</t>
-        </is>
+          <t>Negative electrolyte solute A molarity</t>
+        </is>
+      </c>
+      <c r="B133" s="17" t="n">
+        <v>1</v>
       </c>
       <c r="C133" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D133" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E133" s="17" t="n"/>
       <c r="F133" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B class</t>
+          <t>Negative electrolyte solute A manufacturer</t>
         </is>
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>OrganicAcid</t>
+          <t>Empa</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -4306,29 +4306,25 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="n"/>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B chemical name</t>
+          <t>Negative electrolyte solute A manufacturer productD</t>
         </is>
       </c>
       <c r="B135" s="17" t="inlineStr">
         <is>
-          <t>H4PDTA (1,3-propylenediaminetetraacetic acid)</t>
+          <t>KCrPDTA-Fall-25</t>
         </is>
       </c>
       <c r="C135" s="17" t="inlineStr">
@@ -4338,29 +4334,25 @@
       </c>
       <c r="D135" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="E135" s="17" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E135" s="17" t="n"/>
       <c r="F135" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasAnolyte-hasSolute-hasConstituentA-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B chemical formula</t>
+          <t>Negative electrolyte solute B class</t>
         </is>
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>C11H18N2O8</t>
+          <t>OrganicAcid</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -4375,27 +4367,29 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B purity</t>
-        </is>
-      </c>
-      <c r="B137" s="17" t="n">
-        <v>99</v>
+          <t>Negative electrolyte solute B chemical name</t>
+        </is>
+      </c>
+      <c r="B137" s="17" t="inlineStr">
+        <is>
+          <t>H4PDTA (1,3-propylenediaminetetraacetic acid)</t>
+        </is>
       </c>
       <c r="C137" s="17" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D137" s="17" t="inlineStr">
@@ -4403,22 +4397,26 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E137" s="17" t="n"/>
+      <c r="E137" s="17" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F137" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B purity considered in calculation?</t>
+          <t>Negative electrolyte solute B chemical formula</t>
         </is>
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Purity considered</t>
+          <t>C11H18N2O8</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -4433,27 +4431,27 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>State if purity was considered in concentration calculations or not</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-rdfs:comment</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B molarity</t>
+          <t>Negative electrolyte solute B purity</t>
         </is>
       </c>
       <c r="B139" s="17" t="n">
-        <v>0.1</v>
+        <v>99</v>
       </c>
       <c r="C139" s="17" t="inlineStr">
         <is>
-          <t>mol/L</t>
+          <t>%</t>
         </is>
       </c>
       <c r="D139" s="17" t="inlineStr">
@@ -4464,19 +4462,19 @@
       <c r="E139" s="17" t="n"/>
       <c r="F139" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-Purity</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B manufacturer</t>
+          <t>Negative electrolyte solute B purity considered in calculation?</t>
         </is>
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>SigmaAldrich</t>
+          <t>Purity considered</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -4489,25 +4487,29 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="E140" s="4" t="n"/>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>State if purity was considered in concentration calculations or not</t>
+        </is>
+      </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte solute B manufacturer product ID</t>
+          <t>Negative electrolyte solute B molarity</t>
         </is>
       </c>
       <c r="B141" s="17" t="n">
-        <v>33267</v>
+        <v>0.1</v>
       </c>
       <c r="C141" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mol/L</t>
         </is>
       </c>
       <c r="D141" s="17" t="inlineStr">
@@ -4518,130 +4520,130 @@
       <c r="E141" s="17" t="n"/>
       <c r="F141" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-hasMeasuredProperty-AmountConcentration</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Negative electrolyte volume  </t>
-        </is>
-      </c>
-      <c r="B142" s="4" t="n">
-        <v>10</v>
+          <t>Negative electrolyte solute B manufacturer</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>SigmaAldrich</t>
+        </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E142" s="4" t="n"/>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Volume</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte volume flow rate</t>
+          <t>Negative electrolyte solute B manufacturer product ID</t>
         </is>
       </c>
       <c r="B143" s="17" t="n">
-        <v>60</v>
+        <v>33267</v>
       </c>
       <c r="C143" s="17" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D143" s="17" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E143" s="17" t="n"/>
       <c r="F143" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasAnolyte-hasSolute-hasConstituentB-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte volume flow rate calibration</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>Flow calibrated with cell in series</t>
-        </is>
+          <t>Negative electrolyte volume</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="n">
+        <v>10</v>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>Comment if calibrated differently</t>
-        </is>
-      </c>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="n"/>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate-rdfs:comment</t>
+          <t>hasAnolyte-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte pressure</t>
-        </is>
-      </c>
-      <c r="B145" s="17" t="n"/>
+          <t>Negative electrolyte volume flow rate</t>
+        </is>
+      </c>
+      <c r="B145" s="17" t="n">
+        <v>60</v>
+      </c>
       <c r="C145" s="17" t="inlineStr">
         <is>
-          <t>mbar</t>
+          <t>mL/min</t>
         </is>
       </c>
       <c r="D145" s="17" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E145" s="17" t="n"/>
       <c r="F145" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
+          <t>hasAnolyte-hasMeasuredProperty-VolumeFlowRate</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte conductivity</t>
-        </is>
-      </c>
-      <c r="B146" s="4" t="n">
-        <v>48.4</v>
+          <t>Negative electrolyte volume flow rate calibration</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Flow calibrated with cell in series</t>
+        </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -4649,51 +4651,53 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E146" s="4" t="n"/>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>Comment if calibrated differently</t>
+        </is>
+      </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasAnolyte-hasMeasuredProperty-type|VolumeFlowRate-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte viscosity</t>
-        </is>
-      </c>
-      <c r="B147" s="17" t="n">
-        <v>2.32</v>
-      </c>
+          <t>Negative electrolyte pressure</t>
+        </is>
+      </c>
+      <c r="B147" s="17" t="n"/>
       <c r="C147" s="17" t="inlineStr">
         <is>
-          <t>mPa·s</t>
+          <t>mbar</t>
         </is>
       </c>
       <c r="D147" s="17" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="E147" s="17" t="n"/>
       <c r="F147" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-DynamicViscosity</t>
+          <t>hasAnolyte-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte pH</t>
+          <t>Negative electrolyte conductivity</t>
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>8.699999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>unitless</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -4704,22 +4708,22 @@
       <c r="E148" s="4" t="n"/>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-PH</t>
+          <t>hasAnolyte-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte density</t>
+          <t>Negative electrolyte viscosity</t>
         </is>
       </c>
       <c r="B149" s="17" t="n">
-        <v>1.21</v>
+        <v>2.32</v>
       </c>
       <c r="C149" s="17" t="inlineStr">
         <is>
-          <t>g/cm3</t>
+          <t>mPa·s</t>
         </is>
       </c>
       <c r="D149" s="17" t="inlineStr">
@@ -4730,22 +4734,22 @@
       <c r="E149" s="17" t="n"/>
       <c r="F149" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-Density</t>
+          <t>hasAnolyte-hasMeasuredProperty-DynamicViscosity</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte temperature</t>
+          <t>Negative electrolyte pH</t>
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>23</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>°C</t>
+          <t>unitless</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -4756,22 +4760,22 @@
       <c r="E150" s="4" t="n"/>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
+          <t>hasAnolyte-hasMeasuredProperty-PH</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte tank volume</t>
+          <t>Negative electrolyte density</t>
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>50</v>
+        <v>1.21</v>
       </c>
       <c r="C151" s="17" t="inlineStr">
         <is>
-          <t>mL</t>
+          <t>g/cm3</t>
         </is>
       </c>
       <c r="D151" s="17" t="inlineStr">
@@ -4782,24 +4786,22 @@
       <c r="E151" s="17" t="n"/>
       <c r="F151" s="17" t="inlineStr">
         <is>
-          <t>hasComponent-type|AnolyteTank-hasMeasuredProperty-Volume</t>
+          <t>hasAnolyte-hasMeasuredProperty-Density</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte tank convection?</t>
-        </is>
-      </c>
-      <c r="B152" s="4" t="inlineStr">
-        <is>
-          <t>Bubbled with gas</t>
-        </is>
+          <t>Negative electrolyte temperature</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="n">
+        <v>23</v>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>°C</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -4807,31 +4809,25 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E152" s="4" t="n"/>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|AnolyteTank-rdfs:comment</t>
+          <t>hasAnolyte-hasMeasuredProperty-CelsiusTemperature</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="17" t="inlineStr">
         <is>
-          <t>Negative electrolyte gas</t>
-        </is>
-      </c>
-      <c r="B153" s="17" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
+          <t>Negative electrolyte tank volume</t>
+        </is>
+      </c>
+      <c r="B153" s="17" t="n">
+        <v>50</v>
       </c>
       <c r="C153" s="17" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mL</t>
         </is>
       </c>
       <c r="D153" s="17" t="inlineStr">
@@ -4839,29 +4835,27 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E153" s="17" t="inlineStr">
-        <is>
-          <t>e.g. Argon, Nitrogen, leave empty if none</t>
-        </is>
-      </c>
+      <c r="E153" s="17" t="n"/>
       <c r="F153" s="17" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasConstituent</t>
+          <t>hasComponent-type|AnolyteTank-hasMeasuredProperty-Volume</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Negative electrolyte gas flow rate</t>
-        </is>
-      </c>
-      <c r="B154" s="4" t="n">
-        <v>2.5</v>
+          <t>Negative electrolyte tank convection?</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Bubbled with gas</t>
+        </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>mL/min</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -4869,120 +4863,122 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E154" s="4" t="n"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Describe mode of mixing, bubble with gas, magnetic stirrer, leave empty if none</t>
+        </is>
+      </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>hasAnolyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+          <t>hasComponent-type|AnolyteTank-rdfs:comment</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="17" t="inlineStr">
         <is>
+          <t>Negative electrolyte gas</t>
+        </is>
+      </c>
+      <c r="B155" s="17" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+      <c r="C155" s="17" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E155" s="17" t="inlineStr">
+        <is>
+          <t>e.g. Argon, Nitrogen, leave empty if none</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasConstituent</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Negative electrolyte gas flow rate</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>mL/min</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>hasAnolyte-hasConstituent-hasMeasuredProperty-VolumeFlowRate</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="17" t="inlineStr">
+        <is>
           <t>Negative electrolyte gas pressure</t>
         </is>
       </c>
-      <c r="B155" s="17" t="n">
+      <c r="B157" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="C155" s="17" t="inlineStr">
+      <c r="C157" s="17" t="inlineStr">
         <is>
           <t>mbar</t>
         </is>
       </c>
-      <c r="D155" s="17" t="inlineStr">
+      <c r="D157" s="17" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="E155" s="17" t="n"/>
-      <c r="F155" s="17" t="inlineStr">
+      <c r="E157" s="17" t="n"/>
+      <c r="F157" s="17" t="inlineStr">
         <is>
           <t>hasAnolyte-hasConstituent-hasMeasuredProperty-Pressure</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="18" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="18" t="inlineStr">
         <is>
           <t>Membrane</t>
         </is>
       </c>
-      <c r="B156" s="19" t="n"/>
-      <c r="C156" s="19" t="n"/>
-      <c r="D156" s="19" t="n"/>
-      <c r="E156" s="19" t="n"/>
-      <c r="F156" s="19" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="4" t="inlineStr">
-        <is>
-          <t>Membrane type</t>
-        </is>
-      </c>
-      <c r="B157" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="C157" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>CationExchangeMembrane, AnionExchangeMembrane</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="20" t="inlineStr">
-        <is>
-          <t>Membrane A manufacturer</t>
-        </is>
-      </c>
-      <c r="B158" s="20" t="inlineStr">
-        <is>
-          <t>Fumatech</t>
-        </is>
-      </c>
-      <c r="C158" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D158" s="20" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E158" s="20" t="n"/>
-      <c r="F158" s="20" t="inlineStr">
-        <is>
-          <t>hasSeparator-schema:manufacturer</t>
-        </is>
-      </c>
+      <c r="B158" s="19" t="n"/>
+      <c r="C158" s="19" t="n"/>
+      <c r="D158" s="19" t="n"/>
+      <c r="E158" s="19" t="n"/>
+      <c r="F158" s="19" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Membrane A manufacturer product ID</t>
+          <t>Membrane type</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>E630-K</t>
+          <t>CationExchangeMembrane</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -4992,25 +4988,29 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E159" s="4" t="n"/>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane, AnionExchangeMembrane</t>
+        </is>
+      </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-schema:productID</t>
+          <t>hasSeparator</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="20" t="inlineStr">
         <is>
-          <t>Membrane material A class</t>
+          <t>Membrane A manufacturer</t>
         </is>
       </c>
       <c r="B160" s="20" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>Fumatech</t>
         </is>
       </c>
       <c r="C160" s="20" t="inlineStr">
@@ -5023,26 +5023,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E160" s="20" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E160" s="20" t="n"/>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentA</t>
+          <t>hasSeparator-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Membrane material A chemical name</t>
+          <t>Membrane A manufacturer product ID</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Polyether ether ketone (PEEK)</t>
+          <t>E630-K</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -5055,26 +5051,22 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E161" s="4" t="n"/>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasSeparator-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="20" t="inlineStr">
         <is>
-          <t>Membrane material A chemical formula</t>
+          <t>Membrane material A class</t>
         </is>
       </c>
       <c r="B162" s="20" t="inlineStr">
         <is>
-          <t>(C19H12O3)n</t>
+          <t>PolyetherEtherKetone</t>
         </is>
       </c>
       <c r="C162" s="20" t="inlineStr">
@@ -5084,27 +5076,31 @@
       </c>
       <c r="D162" s="20" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E162" s="20" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasSeparator-hasConstituentA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Membrane material B class</t>
-        </is>
-      </c>
-      <c r="B163" s="4" t="n"/>
+          <t>Membrane material A chemical name</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Polyether ether ketone (PEEK)</t>
+        </is>
+      </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5112,27 +5108,31 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Ontology term, be as specific as possible</t>
+          <t>Important if specific ontology class not available</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentB</t>
+          <t>hasSeparator-hasConstituentA-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="20" t="inlineStr">
         <is>
-          <t>Membrane material B chemical name</t>
-        </is>
-      </c>
-      <c r="B164" s="20" t="n"/>
+          <t>Membrane material A chemical formula</t>
+        </is>
+      </c>
+      <c r="B164" s="20" t="inlineStr">
+        <is>
+          <t>(C19H12O3)n</t>
+        </is>
+      </c>
       <c r="C164" s="20" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D164" s="20" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E164" s="20" t="inlineStr">
@@ -5150,14 +5150,14 @@
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasSeparator-hasConstituentA-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Membrane material B chemical formula</t>
+          <t>Membrane material B class</t>
         </is>
       </c>
       <c r="B165" s="4" t="n"/>
@@ -5173,77 +5173,83 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasSeparator-hasConstituentB</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="20" t="inlineStr">
         <is>
-          <t>Membrane thickness</t>
-        </is>
-      </c>
-      <c r="B166" s="20" t="n">
-        <v>30</v>
-      </c>
+          <t>Membrane material B chemical name</t>
+        </is>
+      </c>
+      <c r="B166" s="20" t="n"/>
       <c r="C166" s="20" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D166" s="20" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E166" s="20" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F166" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-Thickness</t>
+          <t>hasSeparator-hasConstituentB-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Membrane area specific conductivity</t>
+          <t>Membrane material B chemical formula</t>
         </is>
       </c>
       <c r="B167" s="4" t="n"/>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>mS/cm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
-        </is>
-      </c>
-      <c r="E167" s="4" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-ElectrolyticConductivity</t>
+          <t>hasSeparator-hasConstituentB-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="20" t="inlineStr">
         <is>
-          <t>Membrane projected area</t>
+          <t>Membrane thickness</t>
         </is>
       </c>
       <c r="B168" s="20" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C168" s="20" t="inlineStr">
         <is>
-          <t>cm2</t>
+          <t>um</t>
         </is>
       </c>
       <c r="D168" s="20" t="inlineStr">
@@ -5254,24 +5260,20 @@
       <c r="E168" s="20" t="n"/>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>hasSeparator-hasMeasuredProperty-Area</t>
+          <t>hasSeparator-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane storage </t>
-        </is>
-      </c>
-      <c r="B169" s="4" t="inlineStr">
-        <is>
-          <t>Water, &gt;24 h, room temperature</t>
-        </is>
-      </c>
+          <t>Membrane area specific conductivity</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="n"/>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>mS/cm</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5279,130 +5281,124 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>Describe membrane storage conditions (medium, duration, temperature)</t>
-        </is>
-      </c>
+      <c r="E169" s="4" t="n"/>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>hasSeparator-rdfs:comment</t>
+          <t>hasSeparator-hasMeasuredProperty-ElectrolyticConductivity</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane pre-treatment </t>
-        </is>
-      </c>
-      <c r="B170" s="20" t="inlineStr">
+          <t>Membrane projected area</t>
+        </is>
+      </c>
+      <c r="B170" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="C170" s="20" t="inlineStr">
+        <is>
+          <t>cm2</t>
+        </is>
+      </c>
+      <c r="D170" s="20" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E170" s="20" t="n"/>
+      <c r="F170" s="20" t="inlineStr">
+        <is>
+          <t>hasSeparator-hasMeasuredProperty-Area</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Membrane storage</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Water, &gt;24 h, room temperature</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D171" s="4" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>Describe membrane storage conditions (medium, duration, temperature)</t>
+        </is>
+      </c>
+      <c r="F171" s="4" t="inlineStr">
+        <is>
+          <t>hasSeparator-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="20" t="inlineStr">
+        <is>
+          <t>Membrane pre-treatment</t>
+        </is>
+      </c>
+      <c r="B172" s="20" t="inlineStr">
         <is>
           <t>Untreated membrane</t>
         </is>
       </c>
-      <c r="C170" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D170" s="20" t="inlineStr">
+      <c r="C172" s="20" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D172" s="20" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E170" s="20" t="inlineStr">
+      <c r="E172" s="20" t="inlineStr">
         <is>
           <t>Describe membrane pre-treatment conditions (medium, duration, temperature)</t>
         </is>
       </c>
-      <c r="F170" s="20" t="inlineStr">
+      <c r="F172" s="20" t="inlineStr">
         <is>
           <t>hasSeparator-rdfs:comment</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Cell assembly</t>
         </is>
       </c>
-      <c r="B171" s="3" t="n"/>
-      <c r="C171" s="3" t="n"/>
-      <c r="D171" s="3" t="n"/>
-      <c r="E171" s="3" t="n"/>
-      <c r="F171" s="3" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="inlineStr">
-        <is>
-          <t>Cell case type</t>
-        </is>
-      </c>
-      <c r="B172" s="4" t="inlineStr">
-        <is>
-          <t>FlowCell</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D172" s="4" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E172" s="4" t="n"/>
-      <c r="F172" s="4" t="inlineStr">
-        <is>
-          <t>hasCase</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="5" t="inlineStr">
-        <is>
-          <t>Cell case manufacturer</t>
-        </is>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>Fuel Cell Technologies</t>
-        </is>
-      </c>
-      <c r="C173" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>Fuel Cell Technologies, Pinflow, etc.</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>hasCase-schema:manufacturer</t>
-        </is>
-      </c>
+      <c r="B173" s="3" t="n"/>
+      <c r="C173" s="3" t="n"/>
+      <c r="D173" s="3" t="n"/>
+      <c r="E173" s="3" t="n"/>
+      <c r="F173" s="3" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Cell case manufacturer product ID</t>
+          <t>Cell case type</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>5SCH</t>
+          <t>FlowCell</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
@@ -5412,25 +5408,25 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E174" s="4" t="n"/>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>hasCase-schema:productID</t>
+          <t>hasCase</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="inlineStr">
         <is>
-          <t>Flowfield material class</t>
+          <t>Cell case manufacturer</t>
         </is>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Fuel Cell Technologies</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
@@ -5445,24 +5441,24 @@
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Ontology term, be as specific as possible</t>
+          <t>Fuel Cell Technologies, Pinflow, etc.</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField</t>
+          <t>hasCase-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Flowfield material chemical name</t>
+          <t>Cell case manufacturer product ID</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>5SCH</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
@@ -5472,29 +5468,25 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>required</t>
-        </is>
-      </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n"/>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasCase-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
-          <t>Flowfield materail chemical formula</t>
+          <t>Flowfield material class</t>
         </is>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
@@ -5509,24 +5501,24 @@
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasComponent-type|FlowField</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Flowfield type</t>
+          <t>Flowfield material chemical name</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Serpentine</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
@@ -5539,22 +5531,26 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E178" s="4" t="n"/>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-schema:description</t>
+          <t>hasComponent-type|FlowField-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
         <is>
-          <t>Flowfield manufacturer</t>
+          <t>Flowfield material chemical formula</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -5567,22 +5563,26 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n"/>
+      <c r="E179" s="5" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-schema:manufacturer</t>
+          <t>hasComponent-type|FlowField-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Flowfield manufacturer product ID</t>
+          <t>Flowfield type</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>5SCH-PB</t>
+          <t>Serpentine</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E180" s="4" t="n"/>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|FlowField-schema:productID</t>
+          <t>hasComponent-type|FlowField-schema:description</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="5" t="inlineStr">
         <is>
-          <t>Gasket material class</t>
+          <t>Flowfield manufacturer</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>PolymerCompound</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
@@ -5623,26 +5623,22 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E181" s="5" t="inlineStr">
-        <is>
-          <t>Ontology term, be as specific as possible</t>
-        </is>
-      </c>
+      <c r="E181" s="5" t="n"/>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket</t>
+          <t>hasComponent-type|FlowField-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Gasket material chemical name</t>
+          <t>Flowfield manufacturer product ID</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Viton</t>
+          <t>5SCH-PB</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -5655,24 +5651,24 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>Important if specific ontology class not available</t>
-        </is>
-      </c>
+      <c r="E182" s="4" t="n"/>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-hasDatumA-type|ChemicalName-hasStringValue</t>
+          <t>hasComponent-type|FlowField-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="5" t="inlineStr">
         <is>
-          <t>Gasket material chemical formula</t>
-        </is>
-      </c>
-      <c r="B183" s="5" t="n"/>
+          <t>Gasket material class</t>
+        </is>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>PolymerCompound</t>
+        </is>
+      </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5680,29 +5676,29 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>recommended</t>
+          <t>required</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Important if specific ontology class not available</t>
+          <t>Ontology term, be as specific as possible</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-hasDatumB-type|ChemicalFormula-hasStringValue</t>
+          <t>hasComponent-type|Gasket</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Gasket manufacturer</t>
+          <t>Gasket material chemical name</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Maagtechnic AG</t>
+          <t>Viton</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
@@ -5715,22 +5711,24 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E184" s="4" t="n"/>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-schema:manufacturer</t>
+          <t>hasComponent-type|Gasket-hasDatumA-type|ChemicalName-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="5" t="inlineStr">
         <is>
-          <t>Gasket manufacturer product ID</t>
-        </is>
-      </c>
-      <c r="B185" s="5" t="n">
-        <v>17965343</v>
-      </c>
+          <t>Gasket material chemical formula</t>
+        </is>
+      </c>
+      <c r="B185" s="5" t="n"/>
       <c r="C185" s="5" t="inlineStr">
         <is>
           <t>No Unit</t>
@@ -5741,51 +5739,57 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E185" s="5" t="n"/>
+      <c r="E185" s="5" t="inlineStr">
+        <is>
+          <t>Important if specific ontology class not available</t>
+        </is>
+      </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Gasket-schema:productID</t>
+          <t>hasComponent-type|Gasket-hasDatumB-type|ChemicalFormula-hasStringValue</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Gasket thickness</t>
-        </is>
-      </c>
-      <c r="B186" s="4" t="n">
-        <v>450</v>
+          <t>Gasket manufacturer</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Maagtechnic AG</t>
+        </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>um</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>recommended</t>
         </is>
       </c>
       <c r="E186" s="4" t="n"/>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-hasMeasuredProperty-Thickness</t>
+          <t>hasComponent-type|Gasket-schema:manufacturer</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
         <is>
-          <t>Torque upon assembly</t>
+          <t>Gasket manufacturer product ID</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
-        <v>6</v>
+        <v>17965343</v>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Nm</t>
+          <t>No Unit</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
@@ -5796,24 +5800,22 @@
       <c r="E187" s="5" t="n"/>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>hasCase-hasMeasuredProperty-Torque</t>
+          <t>hasComponent-type|Gasket-schema:productID</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>Connector type</t>
-        </is>
-      </c>
-      <c r="B188" s="4" t="inlineStr">
-        <is>
-          <t>Banana plug connected via crocodile clamp</t>
-        </is>
+          <t>Gasket thickness</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="n">
+        <v>450</v>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>um</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -5821,31 +5823,25 @@
           <t>required</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>Describe cell lead-instrument connection</t>
-        </is>
-      </c>
+      <c r="E188" s="4" t="n"/>
       <c r="F188" s="4" t="inlineStr">
         <is>
-          <t>hasComponent-type|Connector-rdfs:comment</t>
+          <t>hasComponent-hasMeasuredProperty-Thickness</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
         <is>
-          <t>Connection type</t>
-        </is>
-      </c>
-      <c r="B189" s="5" t="inlineStr">
-        <is>
-          <t>4-point</t>
-        </is>
+          <t>Torque upon assembly</t>
+        </is>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>6</v>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>No Unit</t>
+          <t>Nm</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
@@ -5853,42 +5849,102 @@
           <t>recommended</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr">
-        <is>
-          <t>Describe if other mode, e.g. 2-point</t>
-        </is>
-      </c>
+      <c r="E189" s="5" t="n"/>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>hasComponent-type|Connector-rdfs:comment</t>
+          <t>hasCase-hasMeasuredProperty-Torque</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
+          <t>Connector type</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Banana plug connected via crocodile clamp</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D190" s="4" t="inlineStr">
+        <is>
+          <t>required</t>
+        </is>
+      </c>
+      <c r="E190" s="4" t="inlineStr">
+        <is>
+          <t>Describe cell lead-instrument connection</t>
+        </is>
+      </c>
+      <c r="F190" s="4" t="inlineStr">
+        <is>
+          <t>hasComponent-type|Connector-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>Connection type</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>4-point</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>No Unit</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>recommended</t>
+        </is>
+      </c>
+      <c r="E191" s="5" t="inlineStr">
+        <is>
+          <t>Describe if other mode, e.g. 2-point</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>hasComponent-type|Connector-rdfs:comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
           <t>Assembled resistance</t>
         </is>
       </c>
-      <c r="B190" s="4" t="n">
+      <c r="B192" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="C190" s="4" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
         <is>
           <t>ohm</t>
         </is>
       </c>
-      <c r="D190" s="4" t="inlineStr">
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
+      <c r="E192" s="4" t="inlineStr">
         <is>
           <t>Resistance of the as-assembled cell, before any experiments</t>
         </is>
       </c>
-      <c r="F190" s="4" t="inlineStr">
+      <c r="F192" s="4" t="inlineStr">
         <is>
           <t>hasMeasuredProperty-ElectricResistance</t>
         </is>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Extra" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@References" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,9 +36,6 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <sz val="11"/>
     </font>
   </fonts>
@@ -122,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -172,8 +169,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -854,7 +849,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0.1.4</t>
+          <t>0.2.0</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -5967,224 +5962,537 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>Include this info (yes/no) Test becomes root object</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>No</t>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>References</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Example dataset title</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Include references in metadata file (yes/no)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>What the dataset contains, and anything needed to read it correctly.</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>References for dataset</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
-        <is>
-          <t>Keywords</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>redox flow battery</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>electrochemical cell</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset for publication 'Revalidating KCrPDTA for aqueous redox flow batteries'</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>Publisher</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Dataset description</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Data from 62 zero-gap redox flow battery cells featuring the KCrPDTA | K4Fe(CN)6 chemistry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Dataset publisher</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="21" t="inlineStr">
-        <is>
-          <t>License</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Dataset license</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="21" t="inlineStr">
-        <is>
-          <t>Date issued</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
-        <is>
-          <t>Date published</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date issued</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>Publication DOI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1234/example.2026.001</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date published</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Dataset URL</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5281/zenodo.1234567</t>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.21805277</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Dataset API URL</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/api/records/1234567</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/21805277</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>Citation</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>F. Lastname et al., Example Journal 1, 100 (2026).</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorA</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t>Figures</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorB</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorC</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorD</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Lina Camenisch</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorE</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Rohat Celik</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorF</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorG</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Baban Deep Virk</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorH</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorI</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>David Reber</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>References for associated publications</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication DOI</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6eb00156d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication title</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Revalidating KCrPDTA for aqueous redox flow batteries</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication figures</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Fig. 1a</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Fig. 2b</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="21" t="inlineStr">
-        <is>
-          <t>Authors</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>Affiliations</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>Firstname Lastname</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorB</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorC</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorD</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Lina Camenisch</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorE</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Rohat Celik</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorF</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorG</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Baban Deep Virk</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorH</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Corsin Battaglia</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>EPFL</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ETH Zurich</t>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorI</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>David Reber</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6582,230 +6890,338 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>David Reber</t>
+          <t>Baban Deep Virk</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-4426-8717</t>
+          <t>https://orcid.org/0009-0008-4669-0816</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>Corsin Battaglia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
+          <t>https://orcid.org/0000-0002-5003-1134</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EPFL</t>
+          <t>David Reber</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q262760</t>
+          <t>https://orcid.org/0000-0002-4426-8717</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
+          <t>Graham Kimbell</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q11942</t>
+          <t>https://orcid.org/0000-0001-9610-3589</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-1336-468X</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>Lina Camenisch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>https://orcid.org/0009-0003-3635-1216</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Fuel Cell Technologies</t>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-1080-5131</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fumatech</t>
+          <t>Rohat Celik</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
+          <t>https://orcid.org/0009-0003-5121-2222</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0001-4487-0062</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q683116</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TitaniumDioxide</t>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Pinflow</t>
+          <t>University of Bern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q114797344</t>
+          <t>https://www.wikidata.org/wiki/Q659080</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PorousElectrode</t>
+          <t>FlowCell</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SGL Carbon</t>
+          <t>Fuel Cell Store</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q320207</t>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SigmaAldrich</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q680841</t>
+          <t>Fuel Cell Technologies</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Fumatech</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q643674</t>
+          <t>https://www.wikidata.org/wiki/Q30254565</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Graphite</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Viton</t>
+          <t>Bismuth</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>TitaniumDioxide</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PotassiumSaltCompound</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PolymerCompound</t>
+          <t>Pinflow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q114797344</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>OrganicAcid</t>
+          <t>PorousElectrode</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Argon</t>
+          <t>SGL Carbon</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q320207</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>SigmaAldrich</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q680841</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q643674</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Viton</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PolyetherEtherKetone</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PotassiumSaltCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PolymerCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>OrganicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -5962,7 +5962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -6493,6 +6493,92 @@
       <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>References for data files</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Data zip file</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Dataset-rocrate.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Tabular data schema</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>https://w3id.org/battery-data-alliance/ontology/battery-data-format/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Data fileA</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001.bdf.parquet</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Time series electrochemical data as parquet with Battery Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Data fileB</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001.eis.bdf.parquet</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Frequency domain data impedance data as parquet with Battery Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Raw data fileA</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001_GCPL_C01.mpr</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Raw cycling data, Biologic EC-Lab mpr binary format</t>
         </is>
       </c>
     </row>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -6515,7 +6515,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Dataset-rocrate.zip</t>
+          <t>BatteryData.zip</t>
         </is>
       </c>
     </row>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -12,7 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Individuals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6707,7 +6708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6735,29 +6736,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hasAnolyte</t>
+          <t>hasActiveMaterial</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Negative electrolyte/Negolyte</t>
+          <t>ActiveMaterial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hasCase</t>
+          <t>hasAnolyte</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anolyte</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Type of cell (FlowCell, FuelCell, SealedCell)</t>
+          <t>Negative electrolyte/Negolyte</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6770,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
+          <t>Catholyte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6781,117 +6782,141 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hasComponent</t>
+          <t>hasCoating</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Coating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hasConstituent</t>
+          <t>hasNegativeElectrode</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NegativeElectrode</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hasMeasuredProperty</t>
+          <t>hasPositiveElectrode</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PositiveElectrode</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode</t>
+          <t>hasSeparator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>Separator</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Membrane</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hasPositiveElectrode</t>
+          <t>hasSolute</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Electrode</t>
+          <t>Solute</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Membrane</t>
+          <t>hasSolvent</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solvent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hasSolute</t>
+          <t>hasSubstrate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Solute</t>
+          <t>Substrate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Carbon, CarbonPaper, CarbonFelt, CarbonCloth</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hasSolvent</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Solvent</t>
+          <t>hasCase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Type of cell (FlowCell, FuelCell, SealedCell)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hasStringValue</t>
+          <t>hasComponent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hasSubstrate</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Substrate</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Carbon, CarbonPaper, CarbonFelt, CarbonCloth</t>
+          <t>hasConstituent</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hasCoating</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Coating</t>
+          <t>hasDatum</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>hasMeasuredProperty</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>hasStringValue</t>
         </is>
       </c>
     </row>
@@ -6906,26 +6931,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
@@ -6937,6 +6956,11 @@
           <t>AnionExchangeMembrane</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6976,338 +7000,96 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Baban Deep Virk</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0008-4669-0816</t>
+          <t>FlowCell</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Corsin Battaglia</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-5003-1134</t>
+          <t>Graphite</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>David Reber</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-4426-8717</t>
+          <t>Bismuth</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Graham Kimbell</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0001-9610-3589</t>
+          <t>TitaniumDioxide</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jeonghoon Ahn</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0003-1336-468X</t>
+          <t>Electrocatalyst</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lina Camenisch</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0003-3635-1216</t>
+          <t>PorousElectrode</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Qirui Liu</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0000-0002-1080-5131</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rohat Celik</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0003-5121-2222</t>
+          <t>PolyetherEtherKetone</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Talia Echeverria</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://orcid.org/0009-0001-4487-0062</t>
+          <t>PotassiumSaltCompound</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Empa</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
+          <t>PolymerCompound</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EPFL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q262760</t>
+          <t>OrganicAcid</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ETH Zurich</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q11942</t>
+          <t>Argon</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>University of Bern</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q659080</t>
+          <t>Nitrogen</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
-        <is>
-          <t>FlowCell</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Fuel Cell Store</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Fuel Cell Technologies</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Fumatech</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Graphite</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Bismuth</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TitaniumDioxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Electrocatalyst</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pinflow</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q114797344</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>PorousElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SGL Carbon</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q320207</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>SigmaAldrich</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q680841</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q643674</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Viton</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>PolyetherEtherKetone</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>PolymerCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>OrganicAcid</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Nitrogen</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
         <is>
           <t>Gas</t>
         </is>
@@ -7319,6 +7101,383 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baban Deep Virk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0008-4669-0816</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-5003-1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>David Reber</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-4426-8717</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-9610-3589</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-1336-468X</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lina Camenisch</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-3635-1216</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-1080-5131</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rohat Celik</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-5121-2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0001-4487-0062</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q683116</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q262760</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q11942</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q659080</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q27868725</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fumatech</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q30254565</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pinflow</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q114797344</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SGL Carbon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q320207</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SigmaAldrich</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q680841</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://www.wikidata.org/wiki/Q643674</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fuel Cell Technologies</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -601,11 +601,7 @@
           <t>RedoxFlowBattery</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -633,11 +629,7 @@
           <t>empa_fcid_000001</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -665,11 +657,7 @@
           <t>260501_reda_1M-KCrPDTA_01</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -697,11 +685,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -729,11 +713,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -761,11 +741,7 @@
           <t>David Reber</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -793,11 +769,7 @@
           <t>SNSF Ambizione Z00P2_209078</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -821,11 +793,7 @@
           <t>RFBCellSchema</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -853,11 +821,7 @@
           <t>0.2.0</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -897,11 +861,7 @@
           <t>PorousElectrode</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -925,11 +885,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -953,11 +909,7 @@
           <t>Pristine</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -981,11 +933,7 @@
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -1013,11 +961,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1045,11 +989,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -1077,11 +1017,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1109,11 +1045,7 @@
           <t>SGL Carbon</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -1137,11 +1069,7 @@
           <t>Sigracet 39AA</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1191,11 +1119,7 @@
           <t>Used two 280 µm carbon papers</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1301,11 +1225,7 @@
           <t>Thickness under compression</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -1355,11 +1275,7 @@
           <t>Untreated electrode</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1387,11 +1303,7 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1415,11 +1327,7 @@
           <t>TitaniumDioxide</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1447,11 +1355,7 @@
           <t>Titanium dioxide</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1479,11 +1383,7 @@
           <t>TiO2</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1511,11 +1411,7 @@
           <t>Liquid-phase deposition using a mixed solution of H3BO3 and (NH4)2TiF6</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1581,11 +1477,7 @@
           <t>PorousElectrode</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1609,11 +1501,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1637,11 +1525,7 @@
           <t>Pristine</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -1665,11 +1549,7 @@
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1697,11 +1577,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1729,11 +1605,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1761,11 +1633,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1793,11 +1661,7 @@
           <t>SGL Carbon</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1821,11 +1685,7 @@
           <t>Sigracet 39AA</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1875,11 +1735,7 @@
           <t>Used two 280 µm carbon papers</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1985,11 +1841,7 @@
           <t>Thickness under compression</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2039,11 +1891,7 @@
           <t>Untreated electrode</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2071,11 +1919,7 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C54" s="11" t="n"/>
       <c r="D54" s="11" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2099,11 +1943,7 @@
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2131,11 +1971,7 @@
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C56" s="11" t="n"/>
       <c r="D56" s="11" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2163,11 +1999,7 @@
           <t>Bi</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2195,11 +2027,7 @@
           <t>Deposited from BiCl3 solution</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C58" s="11" t="n"/>
       <c r="D58" s="11" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2265,11 +2093,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2293,11 +2117,7 @@
           <t>Posolyte 0.5M</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C62" s="14" t="n"/>
       <c r="D62" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2321,11 +2141,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2353,11 +2169,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C64" s="14" t="n"/>
       <c r="D64" s="14" t="inlineStr">
         <is>
           <t>required</t>
@@ -2385,11 +2197,7 @@
           <t>H2O</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2443,11 +2251,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2501,11 +2305,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2529,11 +2329,7 @@
           <t>MilliQ</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C70" s="14" t="n"/>
       <c r="D70" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2553,11 +2349,7 @@
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2581,11 +2373,7 @@
         </is>
       </c>
       <c r="B72" s="14" t="n"/>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C72" s="14" t="n"/>
       <c r="D72" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2609,11 +2397,7 @@
         </is>
       </c>
       <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2661,11 +2445,7 @@
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2715,11 +2495,7 @@
         </is>
       </c>
       <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2739,11 +2515,7 @@
         </is>
       </c>
       <c r="B78" s="14" t="n"/>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C78" s="14" t="n"/>
       <c r="D78" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2767,11 +2539,7 @@
           <t>PotassiumSaltCompound</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2799,11 +2567,7 @@
           <t>Potassium ferrocyanide trihydrate</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C80" s="14" t="n"/>
       <c r="D80" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2831,11 +2595,7 @@
           <t>K4Fe(CN)6 * 3 H2O</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2889,11 +2649,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2947,11 +2703,7 @@
           <t>Thermo Fisher Scientific</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C85" s="4" t="n"/>
       <c r="D85" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2973,11 +2725,7 @@
       <c r="B86" s="14" t="n">
         <v>10504474</v>
       </c>
-      <c r="C86" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C86" s="14" t="n"/>
       <c r="D86" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3001,11 +2749,7 @@
           <t>PotassiumSaltCompound</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C87" s="4" t="n"/>
       <c r="D87" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3033,11 +2777,7 @@
           <t>Potassium ferricyanide</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C88" s="14" t="n"/>
       <c r="D88" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3065,11 +2805,7 @@
           <t>K3Fe(CN)6</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C89" s="4" t="n"/>
       <c r="D89" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3123,11 +2859,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3181,11 +2913,7 @@
           <t>Thermo Fisher Scientific</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C93" s="4" t="n"/>
       <c r="D93" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3207,11 +2935,7 @@
       <c r="B94" s="14" t="n">
         <v>10266370</v>
       </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C94" s="14" t="n"/>
       <c r="D94" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3287,11 +3011,7 @@
           <t>Flow calibrated with cell in series</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3499,11 +3219,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C105" s="4" t="n"/>
       <c r="D105" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3527,11 +3243,7 @@
         </is>
       </c>
       <c r="B106" s="14" t="n"/>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C106" s="14" t="n"/>
       <c r="D106" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3619,11 +3331,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C110" s="4" t="n"/>
       <c r="D110" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -3647,11 +3355,7 @@
           <t>Negolyte 1M</t>
         </is>
       </c>
-      <c r="C111" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C111" s="17" t="n"/>
       <c r="D111" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3675,11 +3379,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C112" s="4" t="n"/>
       <c r="D112" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -3707,11 +3407,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C113" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C113" s="17" t="n"/>
       <c r="D113" s="17" t="inlineStr">
         <is>
           <t>required</t>
@@ -3739,11 +3435,7 @@
           <t>H2O</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C114" s="4" t="n"/>
       <c r="D114" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -3797,11 +3489,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C116" s="4" t="n"/>
       <c r="D116" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3855,11 +3543,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3883,11 +3567,7 @@
           <t>MilliQ</t>
         </is>
       </c>
-      <c r="C119" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C119" s="17" t="n"/>
       <c r="D119" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3907,11 +3587,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C120" s="4" t="n"/>
       <c r="D120" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3935,11 +3611,7 @@
         </is>
       </c>
       <c r="B121" s="17" t="n"/>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C121" s="17" t="n"/>
       <c r="D121" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3963,11 +3635,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n"/>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C122" s="4" t="n"/>
       <c r="D122" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4015,11 +3683,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C124" s="4" t="n"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4069,11 +3733,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4093,11 +3753,7 @@
         </is>
       </c>
       <c r="B127" s="17" t="n"/>
-      <c r="C127" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C127" s="17" t="n"/>
       <c r="D127" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4121,11 +3777,7 @@
           <t>PotassiumSaltCompound</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C128" s="4" t="n"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -4153,11 +3805,7 @@
           <t>KCrPDTA * 2 H2O (potassium [1,3-propylenediaminetetraacetato]chromate(III) dihydrate)</t>
         </is>
       </c>
-      <c r="C129" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C129" s="17" t="n"/>
       <c r="D129" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4185,11 +3833,7 @@
           <t>KCrC11H18N2O10</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4243,11 +3887,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4301,11 +3941,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C134" s="4" t="n"/>
       <c r="D134" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4329,11 +3965,7 @@
           <t>KCrPDTA-Fall-25</t>
         </is>
       </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C135" s="17" t="n"/>
       <c r="D135" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4357,11 +3989,7 @@
           <t>OrganicAcid</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4389,11 +4017,7 @@
           <t>H4PDTA (1,3-propylenediaminetetraacetic acid)</t>
         </is>
       </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C137" s="17" t="n"/>
       <c r="D137" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4421,11 +4045,7 @@
           <t>C11H18N2O8</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4479,11 +4099,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C140" s="4" t="n"/>
       <c r="D140" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4537,11 +4153,7 @@
           <t>SigmaAldrich</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C142" s="4" t="n"/>
       <c r="D142" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4563,11 +4175,7 @@
       <c r="B143" s="17" t="n">
         <v>33267</v>
       </c>
-      <c r="C143" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C143" s="17" t="n"/>
       <c r="D143" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4643,11 +4251,7 @@
           <t>Flow calibrated with cell in series</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C146" s="4" t="n"/>
       <c r="D146" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4855,11 +4459,7 @@
           <t>Bubbled with gas</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4887,11 +4487,7 @@
           <t>Argon</t>
         </is>
       </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C155" s="17" t="n"/>
       <c r="D155" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4983,11 +4579,7 @@
           <t>CationExchangeMembrane</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C159" s="4" t="n"/>
       <c r="D159" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5015,11 +4607,7 @@
           <t>Fumatech</t>
         </is>
       </c>
-      <c r="C160" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C160" s="20" t="n"/>
       <c r="D160" s="20" t="inlineStr">
         <is>
           <t>required</t>
@@ -5043,11 +4631,7 @@
           <t>E630-K</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C161" s="4" t="n"/>
       <c r="D161" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5071,11 +4655,7 @@
           <t>PolyetherEtherKetone</t>
         </is>
       </c>
-      <c r="C162" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C162" s="20" t="n"/>
       <c r="D162" s="20" t="inlineStr">
         <is>
           <t>required</t>
@@ -5103,11 +4683,7 @@
           <t>Polyether ether ketone (PEEK)</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C163" s="4" t="n"/>
       <c r="D163" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5135,11 +4711,7 @@
           <t>(C19H12O3)n</t>
         </is>
       </c>
-      <c r="C164" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C164" s="20" t="n"/>
       <c r="D164" s="20" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5163,11 +4735,7 @@
         </is>
       </c>
       <c r="B165" s="4" t="n"/>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C165" s="4" t="n"/>
       <c r="D165" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -5191,11 +4759,7 @@
         </is>
       </c>
       <c r="B166" s="20" t="n"/>
-      <c r="C166" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C166" s="20" t="n"/>
       <c r="D166" s="20" t="inlineStr">
         <is>
           <t>optional</t>
@@ -5219,11 +4783,7 @@
         </is>
       </c>
       <c r="B167" s="4" t="n"/>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C167" s="4" t="n"/>
       <c r="D167" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -5327,11 +4887,7 @@
           <t>Water, &gt;24 h, room temperature</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5359,11 +4915,7 @@
           <t>Untreated membrane</t>
         </is>
       </c>
-      <c r="C172" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C172" s="20" t="n"/>
       <c r="D172" s="20" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5403,11 +4955,7 @@
           <t>FlowCell</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C174" s="4" t="n"/>
       <c r="D174" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5431,11 +4979,7 @@
           <t>Fuel Cell Technologies</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C175" s="5" t="n"/>
       <c r="D175" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5463,11 +5007,7 @@
           <t>5SCH</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C176" s="4" t="n"/>
       <c r="D176" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5491,11 +5031,7 @@
           <t>Graphite</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C177" s="5" t="n"/>
       <c r="D177" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5523,11 +5059,7 @@
           <t>Graphite</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C178" s="4" t="n"/>
       <c r="D178" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5555,11 +5087,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C179" s="5" t="n"/>
       <c r="D179" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5587,11 +5115,7 @@
           <t>Serpentine</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C180" s="4" t="n"/>
       <c r="D180" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5615,11 +5139,7 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C181" s="5" t="n"/>
       <c r="D181" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5643,11 +5163,7 @@
           <t>5SCH-PB</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C182" s="4" t="n"/>
       <c r="D182" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5671,11 +5187,7 @@
           <t>PolymerCompound</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C183" s="5" t="n"/>
       <c r="D183" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5703,11 +5215,7 @@
           <t>Viton</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C184" s="4" t="n"/>
       <c r="D184" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5731,11 +5239,7 @@
         </is>
       </c>
       <c r="B185" s="5" t="n"/>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C185" s="5" t="n"/>
       <c r="D185" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5763,11 +5267,7 @@
           <t>Maagtechnic AG</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C186" s="4" t="n"/>
       <c r="D186" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5789,11 +5289,7 @@
       <c r="B187" s="5" t="n">
         <v>17965343</v>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C187" s="5" t="n"/>
       <c r="D187" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5869,11 +5365,7 @@
           <t>Banana plug connected via crocodile clamp</t>
         </is>
       </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C190" s="4" t="n"/>
       <c r="D190" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5901,11 +5393,7 @@
           <t>4-point</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C191" s="5" t="n"/>
       <c r="D191" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -6594,22 +6082,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
@@ -6711,20 +6205,20 @@
   <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Predicate</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Default class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6931,7 +6425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6953,145 +6447,516 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AnionExchangeMembrane</t>
+          <t>FlowCell</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
+          <t>Cell and battery types. Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>RedoxFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CarbonCloth</t>
+          <t>VanadiumRedoxFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CarbonFelt</t>
+          <t>IronRedoxFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CarbonPaper</t>
+          <t>ZincBromineFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CationExchangeMembrane</t>
+          <t>AqueousOrganicFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>AqueousMetallicFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>HybridFlowBattery</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bismuth</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TitaniumDioxide</t>
-        </is>
-      </c>
-    </row>
+          <t>MembranelessFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
+          <t>FlowField</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cell components</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PorousElectrode</t>
+          <t>CurrentCollector</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Gasket</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PolyetherEtherKetone</t>
+          <t>Pump</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PolymerCompound</t>
-        </is>
-      </c>
-    </row>
+          <t>Tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OrganicAcid</t>
+          <t>PorousElectrode</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Electrodes and substrates</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argon</t>
+          <t>VanadiumBasedElectrode</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Carbon</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>CarbonFelt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CarbonCloth</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CarbonPaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WovenMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ExpandedMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OpenCellFoam</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Electrocatalyst</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Electrocatalysts and coatings</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bismuth</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TitaniumDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Vanadium</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Redox active species and metals</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VanadiumIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VanadiumIIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VanadiumIVOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VanadiumVOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bromine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Iodine</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AnionExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Membranes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IonExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BilayerMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nafion</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PerfluorocarboxylicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IonomerCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PolyetherEtherKetone</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SulfonatedPolyEtherEtherKetone</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Electrolytes and supporting salts</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SulfuricAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HydrochloricAcidSolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PhosphoricAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PotassiumHydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SodiumHydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PotassiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SodiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PotassiumSaltCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OrganicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PolymerCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
           <t>Gas</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gases</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GasMixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Oxygen</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CarbonDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Air</t>
         </is>
       </c>
     </row>
@@ -7110,7 +6975,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="74" customWidth="1" min="4" max="4"/>
   </cols>
@@ -7123,7 +6988,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -7483,22 +7348,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Unit</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Unit class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -7163,12 +7163,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
+          <t>http://www.wikidata.org/entity/Q683116</t>
         </is>
       </c>
     </row>
@@ -7180,12 +7180,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q262760</t>
+          <t>http://www.wikidata.org/entity/Q262760</t>
         </is>
       </c>
     </row>
@@ -7197,12 +7197,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q11942</t>
+          <t>http://www.wikidata.org/entity/Q11942</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>schema:Organization</t>
+          <t>schema:ResearchOrganization</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q659080</t>
+          <t>http://www.wikidata.org/entity/Q659080</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>http://www.wikidata.org/entity/Q27868725</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
+          <t>http://www.wikidata.org/entity/Q30254565</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q114797344</t>
+          <t>http://www.wikidata.org/entity/Q114797344</t>
         </is>
       </c>
     </row>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q320207</t>
+          <t>http://www.wikidata.org/entity/Q320207</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q680841</t>
+          <t>http://www.wikidata.org/entity/Q680841</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q643674</t>
+          <t>http://www.wikidata.org/entity/Q643674</t>
         </is>
       </c>
     </row>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Organisation that made the cell, value should be in @classes with ID</t>
+          <t>Organisation that made the cell. List it in @Individuals to give it an IRI.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Person that made the cell, value should be in @classes with ID</t>
+          <t>Person that made the cell. List them in @Individuals to give them an ORCID.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -5464,7 +5464,17 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>References</t>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Extra values  -&gt;  affiliations for an author, a description for a data file, or more items for a list</t>
         </is>
       </c>
     </row>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -8,10 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Schema" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@References" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Context" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Predicates" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Classes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Individuals" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="@Units" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -567,7 +569,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Comment</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -599,11 +601,7 @@
           <t>RedoxFlowBattery</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
       <c r="D3" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -631,11 +629,7 @@
           <t>empa_fcid_000001</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -663,11 +657,7 @@
           <t>260501_reda_1M-KCrPDTA_01</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
       <c r="D5" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -695,11 +685,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C6" s="5" t="n"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -727,11 +713,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -739,7 +721,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Organisation that made the cell, value should be in @classes with ID</t>
+          <t>Organisation that made the cell. List it in @Individuals to give it an IRI.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -759,11 +741,7 @@
           <t>David Reber</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -771,7 +749,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>Person that made the cell, value should be in @classes with ID</t>
+          <t>Person that made the cell. List them in @Individuals to give them an ORCID.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -791,11 +769,7 @@
           <t>SNSF Ambizione Z00P2_209078</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -819,11 +793,7 @@
           <t>RFBCellSchema</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n"/>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -848,14 +818,10 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0.1.4</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+          <t>0.2.0</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -895,11 +861,7 @@
           <t>PorousElectrode</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -923,11 +885,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C14" s="8" t="n"/>
       <c r="D14" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -951,11 +909,7 @@
           <t>Pristine</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C15" s="4" t="n"/>
       <c r="D15" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -979,11 +933,7 @@
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C16" s="8" t="n"/>
       <c r="D16" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -1011,11 +961,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C17" s="4" t="n"/>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1043,11 +989,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C18" s="8" t="n"/>
       <c r="D18" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -1075,11 +1017,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C19" s="4" t="n"/>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1107,11 +1045,7 @@
           <t>SGL Carbon</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="inlineStr">
         <is>
           <t>required</t>
@@ -1135,11 +1069,7 @@
           <t>Sigracet 39AA</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1189,11 +1119,7 @@
           <t>Used two 280 µm carbon papers</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C23" s="4" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1299,11 +1225,7 @@
           <t>Thickness under compression</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C27" s="4" t="n"/>
       <c r="D27" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -1353,11 +1275,7 @@
           <t>Untreated electrode</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C29" s="4" t="n"/>
       <c r="D29" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1385,11 +1303,7 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C30" s="8" t="n"/>
       <c r="D30" s="8" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1413,11 +1327,7 @@
           <t>TitaniumDioxide</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1445,11 +1355,7 @@
           <t>Titanium dioxide</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C32" s="8" t="n"/>
       <c r="D32" s="8" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1477,11 +1383,7 @@
           <t>TiO2</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1509,11 +1411,7 @@
           <t>Liquid-phase deposition using a mixed solution of H3BO3 and (NH4)2TiF6</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C34" s="8" t="n"/>
       <c r="D34" s="8" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1579,11 +1477,7 @@
           <t>PorousElectrode</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1607,11 +1501,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C38" s="11" t="n"/>
       <c r="D38" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1635,11 +1525,7 @@
           <t>Pristine</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -1663,11 +1549,7 @@
           <t>CarbonPaper</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C40" s="11" t="n"/>
       <c r="D40" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1695,11 +1577,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C41" s="4" t="n"/>
       <c r="D41" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1727,11 +1605,7 @@
           <t>Carbon</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C42" s="11" t="n"/>
       <c r="D42" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1759,11 +1633,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C43" s="4" t="n"/>
       <c r="D43" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1791,11 +1661,7 @@
           <t>SGL Carbon</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C44" s="11" t="n"/>
       <c r="D44" s="11" t="inlineStr">
         <is>
           <t>required</t>
@@ -1819,11 +1685,7 @@
           <t>Sigracet 39AA</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C45" s="4" t="n"/>
       <c r="D45" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -1873,11 +1735,7 @@
           <t>Used two 280 µm carbon papers</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C47" s="4" t="n"/>
       <c r="D47" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -1983,11 +1841,7 @@
           <t>Thickness under compression</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2037,11 +1891,7 @@
           <t>Untreated electrode</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2069,11 +1919,7 @@
           <t>Electrocatalyst</t>
         </is>
       </c>
-      <c r="C54" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C54" s="11" t="n"/>
       <c r="D54" s="11" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2097,11 +1943,7 @@
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2129,11 +1971,7 @@
           <t>Bismuth</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C56" s="11" t="n"/>
       <c r="D56" s="11" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2161,11 +1999,7 @@
           <t>Bi</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C57" s="4" t="n"/>
       <c r="D57" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2193,11 +2027,7 @@
           <t>Deposited from BiCl3 solution</t>
         </is>
       </c>
-      <c r="C58" s="11" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C58" s="11" t="n"/>
       <c r="D58" s="11" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2263,11 +2093,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2291,11 +2117,7 @@
           <t>Posolyte 0.5M</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C62" s="14" t="n"/>
       <c r="D62" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2319,11 +2141,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C63" s="4" t="n"/>
       <c r="D63" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2351,11 +2169,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C64" s="14" t="n"/>
       <c r="D64" s="14" t="inlineStr">
         <is>
           <t>required</t>
@@ -2383,11 +2197,7 @@
           <t>H2O</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2441,11 +2251,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C67" s="4" t="n"/>
       <c r="D67" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2499,11 +2305,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C69" s="4" t="n"/>
       <c r="D69" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2527,11 +2329,7 @@
           <t>MilliQ</t>
         </is>
       </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C70" s="14" t="n"/>
       <c r="D70" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2551,11 +2349,7 @@
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C71" s="4" t="n"/>
       <c r="D71" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2579,11 +2373,7 @@
         </is>
       </c>
       <c r="B72" s="14" t="n"/>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C72" s="14" t="n"/>
       <c r="D72" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2607,11 +2397,7 @@
         </is>
       </c>
       <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2659,11 +2445,7 @@
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2713,11 +2495,7 @@
         </is>
       </c>
       <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C77" s="4" t="n"/>
       <c r="D77" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2737,11 +2515,7 @@
         </is>
       </c>
       <c r="B78" s="14" t="n"/>
-      <c r="C78" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C78" s="14" t="n"/>
       <c r="D78" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -2765,11 +2539,7 @@
           <t>PotassiumSaltCompound</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C79" s="4" t="n"/>
       <c r="D79" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -2797,11 +2567,7 @@
           <t>Potassium ferrocyanide trihydrate</t>
         </is>
       </c>
-      <c r="C80" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C80" s="14" t="n"/>
       <c r="D80" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2829,11 +2595,7 @@
           <t>K4Fe(CN)6 * 3 H2O</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C81" s="4" t="n"/>
       <c r="D81" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2887,11 +2649,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C83" s="4" t="n"/>
       <c r="D83" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2945,11 +2703,7 @@
           <t>Thermo Fisher Scientific</t>
         </is>
       </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C85" s="4" t="n"/>
       <c r="D85" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2971,11 +2725,7 @@
       <c r="B86" s="14" t="n">
         <v>10504474</v>
       </c>
-      <c r="C86" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C86" s="14" t="n"/>
       <c r="D86" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -2999,11 +2749,7 @@
           <t>PotassiumSaltCompound</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C87" s="4" t="n"/>
       <c r="D87" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3031,11 +2777,7 @@
           <t>Potassium ferricyanide</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C88" s="14" t="n"/>
       <c r="D88" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3063,11 +2805,7 @@
           <t>K3Fe(CN)6</t>
         </is>
       </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C89" s="4" t="n"/>
       <c r="D89" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3121,11 +2859,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C91" s="4" t="n"/>
       <c r="D91" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3179,11 +2913,7 @@
           <t>Thermo Fisher Scientific</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C93" s="4" t="n"/>
       <c r="D93" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3205,11 +2935,7 @@
       <c r="B94" s="14" t="n">
         <v>10266370</v>
       </c>
-      <c r="C94" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C94" s="14" t="n"/>
       <c r="D94" s="14" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3285,11 +3011,7 @@
           <t>Flow calibrated with cell in series</t>
         </is>
       </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C97" s="4" t="n"/>
       <c r="D97" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3497,11 +3219,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C105" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C105" s="4" t="n"/>
       <c r="D105" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3525,11 +3243,7 @@
         </is>
       </c>
       <c r="B106" s="14" t="n"/>
-      <c r="C106" s="14" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C106" s="14" t="n"/>
       <c r="D106" s="14" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3617,11 +3331,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C110" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C110" s="4" t="n"/>
       <c r="D110" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -3645,11 +3355,7 @@
           <t>Negolyte 1M</t>
         </is>
       </c>
-      <c r="C111" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C111" s="17" t="n"/>
       <c r="D111" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3673,11 +3379,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C112" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C112" s="4" t="n"/>
       <c r="D112" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -3705,11 +3407,7 @@
           <t>Water</t>
         </is>
       </c>
-      <c r="C113" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C113" s="17" t="n"/>
       <c r="D113" s="17" t="inlineStr">
         <is>
           <t>required</t>
@@ -3737,11 +3435,7 @@
           <t>H2O</t>
         </is>
       </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C114" s="4" t="n"/>
       <c r="D114" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -3795,11 +3489,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C116" s="4" t="n"/>
       <c r="D116" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3853,11 +3543,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C118" s="4" t="n"/>
       <c r="D118" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -3881,11 +3567,7 @@
           <t>MilliQ</t>
         </is>
       </c>
-      <c r="C119" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C119" s="17" t="n"/>
       <c r="D119" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3905,11 +3587,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C120" s="4" t="n"/>
       <c r="D120" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3933,11 +3611,7 @@
         </is>
       </c>
       <c r="B121" s="17" t="n"/>
-      <c r="C121" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C121" s="17" t="n"/>
       <c r="D121" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -3961,11 +3635,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n"/>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C122" s="4" t="n"/>
       <c r="D122" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4013,11 +3683,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C124" s="4" t="n"/>
       <c r="D124" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4067,11 +3733,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C126" s="4" t="n"/>
       <c r="D126" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4091,11 +3753,7 @@
         </is>
       </c>
       <c r="B127" s="17" t="n"/>
-      <c r="C127" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C127" s="17" t="n"/>
       <c r="D127" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4119,11 +3777,7 @@
           <t>PotassiumSaltCompound</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C128" s="4" t="n"/>
       <c r="D128" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -4151,11 +3805,7 @@
           <t>KCrPDTA * 2 H2O (potassium [1,3-propylenediaminetetraacetato]chromate(III) dihydrate)</t>
         </is>
       </c>
-      <c r="C129" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C129" s="17" t="n"/>
       <c r="D129" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4183,11 +3833,7 @@
           <t>KCrC11H18N2O10</t>
         </is>
       </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C130" s="4" t="n"/>
       <c r="D130" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4241,11 +3887,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C132" s="4" t="n"/>
       <c r="D132" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4299,11 +3941,7 @@
           <t>Empa</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C134" s="4" t="n"/>
       <c r="D134" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4327,11 +3965,7 @@
           <t>KCrPDTA-Fall-25</t>
         </is>
       </c>
-      <c r="C135" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C135" s="17" t="n"/>
       <c r="D135" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4355,11 +3989,7 @@
           <t>OrganicAcid</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4387,11 +4017,7 @@
           <t>H4PDTA (1,3-propylenediaminetetraacetic acid)</t>
         </is>
       </c>
-      <c r="C137" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C137" s="17" t="n"/>
       <c r="D137" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4419,11 +4045,7 @@
           <t>C11H18N2O8</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4477,11 +4099,7 @@
           <t>Purity considered</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C140" s="4" t="n"/>
       <c r="D140" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4535,11 +4153,7 @@
           <t>SigmaAldrich</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C142" s="4" t="n"/>
       <c r="D142" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4561,11 +4175,7 @@
       <c r="B143" s="17" t="n">
         <v>33267</v>
       </c>
-      <c r="C143" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C143" s="17" t="n"/>
       <c r="D143" s="17" t="inlineStr">
         <is>
           <t>optional</t>
@@ -4641,11 +4251,7 @@
           <t>Flow calibrated with cell in series</t>
         </is>
       </c>
-      <c r="C146" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C146" s="4" t="n"/>
       <c r="D146" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4853,11 +4459,7 @@
           <t>Bubbled with gas</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4885,11 +4487,7 @@
           <t>Argon</t>
         </is>
       </c>
-      <c r="C155" s="17" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C155" s="17" t="n"/>
       <c r="D155" s="17" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -4981,11 +4579,7 @@
           <t>CationExchangeMembrane</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C159" s="4" t="n"/>
       <c r="D159" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5013,11 +4607,7 @@
           <t>Fumatech</t>
         </is>
       </c>
-      <c r="C160" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C160" s="20" t="n"/>
       <c r="D160" s="20" t="inlineStr">
         <is>
           <t>required</t>
@@ -5041,11 +4631,7 @@
           <t>E630-K</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C161" s="4" t="n"/>
       <c r="D161" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5069,11 +4655,7 @@
           <t>PolyetherEtherKetone</t>
         </is>
       </c>
-      <c r="C162" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C162" s="20" t="n"/>
       <c r="D162" s="20" t="inlineStr">
         <is>
           <t>required</t>
@@ -5101,11 +4683,7 @@
           <t>Polyether ether ketone (PEEK)</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C163" s="4" t="n"/>
       <c r="D163" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5133,11 +4711,7 @@
           <t>(C19H12O3)n</t>
         </is>
       </c>
-      <c r="C164" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C164" s="20" t="n"/>
       <c r="D164" s="20" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5161,11 +4735,7 @@
         </is>
       </c>
       <c r="B165" s="4" t="n"/>
-      <c r="C165" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C165" s="4" t="n"/>
       <c r="D165" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -5189,11 +4759,7 @@
         </is>
       </c>
       <c r="B166" s="20" t="n"/>
-      <c r="C166" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C166" s="20" t="n"/>
       <c r="D166" s="20" t="inlineStr">
         <is>
           <t>optional</t>
@@ -5217,11 +4783,7 @@
         </is>
       </c>
       <c r="B167" s="4" t="n"/>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C167" s="4" t="n"/>
       <c r="D167" s="4" t="inlineStr">
         <is>
           <t>optional</t>
@@ -5325,11 +4887,7 @@
           <t>Water, &gt;24 h, room temperature</t>
         </is>
       </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C171" s="4" t="n"/>
       <c r="D171" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5357,11 +4915,7 @@
           <t>Untreated membrane</t>
         </is>
       </c>
-      <c r="C172" s="20" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C172" s="20" t="n"/>
       <c r="D172" s="20" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5401,11 +4955,7 @@
           <t>FlowCell</t>
         </is>
       </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C174" s="4" t="n"/>
       <c r="D174" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5429,11 +4979,7 @@
           <t>Fuel Cell Technologies</t>
         </is>
       </c>
-      <c r="C175" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C175" s="5" t="n"/>
       <c r="D175" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5461,11 +5007,7 @@
           <t>5SCH</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C176" s="4" t="n"/>
       <c r="D176" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5489,11 +5031,7 @@
           <t>Graphite</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C177" s="5" t="n"/>
       <c r="D177" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5521,11 +5059,7 @@
           <t>Graphite</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C178" s="4" t="n"/>
       <c r="D178" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5553,11 +5087,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C179" s="5" t="n"/>
       <c r="D179" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5585,11 +5115,7 @@
           <t>Serpentine</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C180" s="4" t="n"/>
       <c r="D180" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5613,11 +5139,7 @@
           <t>Fuel Cell Store</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C181" s="5" t="n"/>
       <c r="D181" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5641,11 +5163,7 @@
           <t>5SCH-PB</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C182" s="4" t="n"/>
       <c r="D182" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5669,11 +5187,7 @@
           <t>PolymerCompound</t>
         </is>
       </c>
-      <c r="C183" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C183" s="5" t="n"/>
       <c r="D183" s="5" t="inlineStr">
         <is>
           <t>required</t>
@@ -5701,11 +5215,7 @@
           <t>Viton</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C184" s="4" t="n"/>
       <c r="D184" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5729,11 +5239,7 @@
         </is>
       </c>
       <c r="B185" s="5" t="n"/>
-      <c r="C185" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C185" s="5" t="n"/>
       <c r="D185" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5761,11 +5267,7 @@
           <t>Maagtechnic AG</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C186" s="4" t="n"/>
       <c r="D186" s="4" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5787,11 +5289,7 @@
       <c r="B187" s="5" t="n">
         <v>17965343</v>
       </c>
-      <c r="C187" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C187" s="5" t="n"/>
       <c r="D187" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5867,11 +5365,7 @@
           <t>Banana plug connected via crocodile clamp</t>
         </is>
       </c>
-      <c r="C190" s="4" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C190" s="4" t="n"/>
       <c r="D190" s="4" t="inlineStr">
         <is>
           <t>required</t>
@@ -5899,11 +5393,7 @@
           <t>4-point</t>
         </is>
       </c>
-      <c r="C191" s="5" t="inlineStr">
-        <is>
-          <t>No Unit</t>
-        </is>
-      </c>
+      <c r="C191" s="5" t="n"/>
       <c r="D191" s="5" t="inlineStr">
         <is>
           <t>recommended</t>
@@ -5961,106 +5451,633 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Extra values  -&gt;  affiliations for an author, a description for a data file, or more items for a list</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://schema.org/</t>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Include references in metadata file (yes/no)</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>emmo</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo#</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>References for dataset</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n"/>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>echem</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo/domain/electrochemistry#</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset name</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Dataset for publication 'Revalidating KCrPDTA for aqueous redox flow batteries'</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo/domain/battery#</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Dataset description</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Data from 62 zero-gap redox flow battery cells featuring the KCrPDTA | K4Fe(CN)6 chemistry.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>chemical</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://w3id.org/emmo/domain/chemical-substance#</t>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Dataset publisher</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://qudt.org/vocab/unit/</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Dataset license</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>https://creativecommons.org/licenses/by/4.0/</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rdfs</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date issued</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Dataset date published</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Dataset URL</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.5281/zenodo.21805277</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Dataset API URL</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/api/records/21805277</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorA</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorB</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorC</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorD</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Lina Camenisch</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorE</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Rohat Celik</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorF</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorG</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Baban Deep Virk</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorH</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Dataset authorI</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>David Reber</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>References for associated publications</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication DOI</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1039/d6eb00156d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication title</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Revalidating KCrPDTA for aqueous redox flow batteries</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication figures</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Fig. 1a</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Fig. 2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorB</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorC</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorD</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Lina Camenisch</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorE</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Rohat Celik</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorF</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorG</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Baban Deep Virk</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorH</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Associated publication authorI</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>David Reber</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>References for data files</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Data zip file</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>BatteryData.zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Tabular data schema</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>https://w3id.org/battery-data-alliance/ontology/battery-data-format/schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Data fileA</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001.bdf.parquet</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Time series electrochemical data as parquet with Battery Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Data fileB</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001.eis.bdf.parquet</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Frequency domain data impedance data as parquet with Battery Data Format columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Raw data fileA</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001_GCPL_C01.mpr</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Raw cycling data, Biologic EC-Lab mpr binary format</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -6086,12 +6103,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Term</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>IRI</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6103,163 +6120,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hasAnolyte</t>
+          <t>schema</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Negative electrolyte/Negolyte</t>
+          <t>https://schema.org/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hasCase</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Type of cell (FlowCell, FuelCell, SealedCell)</t>
+          <t>emmo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://w3id.org/emmo#</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hasCatholyte</t>
+          <t>echem</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Positive electrolyte/Posolyte</t>
+          <t>https://w3id.org/emmo/domain/electrochemistry#</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>hasComponent</t>
+          <t>battery</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://w3id.org/emmo/domain/battery#</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>hasConstituent</t>
+          <t>chemical</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://w3id.org/emmo/domain/chemical-substance#</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>hasMeasuredProperty</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://qudt.org/vocab/unit/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hasNegativeElectrode</t>
+          <t>rdfs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Electrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>hasPositiveElectrode</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Electrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>hasSeparator</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Membrane</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>hasSolute</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Solute</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>hasSolvent</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Solvent</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>hasStringValue</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>hasSubstrate</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Substrate</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Carbon, CarbonPaper, CarbonFelt, CarbonCloth</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>hasCoating</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Coating</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#</t>
         </is>
       </c>
     </row>
@@ -6274,23 +6212,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Predicate</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Default class</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -6302,250 +6240,187 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AnionExchangeMembrane</t>
+          <t>hasActiveMaterial</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ActiveMaterial</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>hasAnolyte</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Anolyte</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Negative electrolyte/Negolyte</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CarbonCloth</t>
+          <t>hasCatholyte</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Catholyte</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Positive electrolyte/Posolyte</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CarbonFelt</t>
+          <t>hasCoating</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Coating</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CarbonPaper</t>
+          <t>hasNegativeElectrode</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NegativeElectrode</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CationExchangeMembrane</t>
+          <t>hasPositiveElectrode</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PositiveElectrode</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>David Reber</t>
+          <t>hasSeparator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://orcid.org/0000-0002-4426-8717</t>
+          <t>Separator</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Membrane</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Empa</t>
+          <t>hasSolute</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q683116</t>
+          <t>Solute</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FlowCell</t>
+          <t>hasSolvent</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solvent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Fuel Cell Store</t>
+          <t>hasSubstrate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.wikidata.org/wiki/Q27868725</t>
+          <t>Substrate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Carbon, CarbonPaper, CarbonFelt, CarbonCloth</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fuel Cell Technologies</t>
+          <t>hasCase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Type of cell (FlowCell, FuelCell, SealedCell)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fumatech</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q30254565</t>
+          <t>hasComponent</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>hasConstituent</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bismuth</t>
+          <t>hasDatum</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TitaniumDioxide</t>
+          <t>hasMeasuredProperty</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Electrocatalyst</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Pinflow</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q114797344</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PorousElectrode</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SGL Carbon</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q320207</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SigmaAldrich</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q680841</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://www.wikidata.org/wiki/Q643674</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Water</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Viton</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PolyetherEtherKetone</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PotassiumSaltCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PolymerCompound</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>OrganicAcid</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Argon</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Nitrogen</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Gas</t>
+          <t>hasStringValue</t>
         </is>
       </c>
     </row>
@@ -6560,22 +6435,951 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Class</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FlowCell</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cell and battery types. Classes available to the @Schema sheet Value column. Classes must already exist in the ontology. You can declare your own custom classes in the @Context sheet. This column is a reference list, a value already known to the ontology works even if it is not listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RedoxFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VanadiumRedoxFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>IronRedoxFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ZincBromineFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AqueousOrganicFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AqueousMetallicFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>HybridFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MembranelessFlowBattery</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FlowField</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cell components</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CurrentCollector</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gasket</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pump</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>PorousElectrode</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Electrodes and substrates</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VanadiumBasedElectrode</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Carbon</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>CarbonFelt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CarbonCloth</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>CarbonPaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WovenMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ExpandedMesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OpenCellFoam</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Electrocatalyst</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Electrocatalysts and coatings</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bismuth</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TitaniumDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Vanadium</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Redox active species and metals</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VanadiumIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VanadiumIIIOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VanadiumIVOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VanadiumVOxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chromium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bromine</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Iodine</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AnionExchangeMembrane</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Membranes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>CationExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IonExchangeMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BilayerMembrane</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Nafion</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PerfluorosulfonicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PerfluorocarboxylicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>IonomerCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PolyetherEtherKetone</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SulfonatedPolyEtherEtherKetone</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Electrolytes and supporting salts</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SulfuricAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HydrochloricAcidSolution</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PhosphoricAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PotassiumHydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SodiumHydroxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PotassiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SodiumChloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PotassiumSaltCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>OrganicAcid</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PolymerCompound</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gases</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>GasMixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Argon</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nitrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Oxygen</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>CarbonDioxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Air</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>IRI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baban Deep Virk</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0008-4669-0816</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Corsin Battaglia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-5003-1134</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>David Reber</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-4426-8717</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Graham Kimbell</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0001-9610-3589</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jeonghoon Ahn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-1336-468X</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lina Camenisch</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-3635-1216</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Qirui Liu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0000-0002-1080-5131</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Rohat Celik</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0003-5121-2222</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Talia Echeverria</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>schema:Person</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://orcid.org/0009-0001-4487-0062</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Empa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q683116</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q262760</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q11942</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>University of Bern</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>schema:ResearchOrganization</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q659080</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Fuel Cell Store</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q27868725</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fumatech</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q30254565</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pinflow</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q114797344</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SGL Carbon</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q320207</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SigmaAldrich</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q680841</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Thermo Fisher Scientific</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>http://www.wikidata.org/entity/Q643674</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fuel Cell Technologies</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>schema:Organization</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unit class</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>

--- a/test/data/flowcell_excel_schema.xlsx
+++ b/test/data/flowcell_excel_schema.xlsx
@@ -818,7 +818,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>0.2.0</t>
+          <t>0.2.1</t>
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
@@ -5451,7 +5451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -6078,6 +6078,23 @@
       <c r="C39" s="4" t="inlineStr">
         <is>
           <t>Raw cycling data, Biologic EC-Lab mpr binary format</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Input fileA</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>empa__fcid000001/empa__fcid000001.mps</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Cycling protocol, Biologic EC-Lab settings file</t>
         </is>
       </c>
     </row>
